--- a/Pull.xlsx
+++ b/Pull.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salimlias\Desktop\Work\Personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36A20CC-E559-4B75-B8DF-7ABC5B01B282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12174C9C-D911-4EBB-974E-F24D99370C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="4" xr2:uid="{D18E24B4-D831-4D2C-A3F7-1212CF31CFC5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{D18E24B4-D831-4D2C-A3F7-1212CF31CFC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Зарплата" sheetId="1" r:id="rId1"/>
@@ -324,9 +324,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
@@ -336,16 +333,7 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -373,7 +361,19 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -418,7 +418,7 @@
   <autoFilter ref="A1:C13" xr:uid="{B7258D4C-C9D1-4881-86D3-220BC9C377BE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{6A7DDB32-BA3A-4445-9F40-BC10A802B82B}" name="Месяц"/>
-    <tableColumn id="2" xr3:uid="{5146812B-65A7-46BA-9B28-6B50403D0380}" name="Сумма" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{5146812B-65A7-46BA-9B28-6B50403D0380}" name="Сумма" dataDxfId="12">
       <calculatedColumnFormula>L3+L4+L6+L7+L8+L9</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4D14FB41-4036-492D-8C52-C609C3CFA4C9}" name="Свободные деньги">
@@ -445,38 +445,38 @@
   <autoFilter ref="A1:H169" xr:uid="{9E19A74D-DF9C-49FE-8C8C-971945A1577F}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{800BB357-AD45-4907-94F8-698FB032A955}" name="Месяц"/>
-    <tableColumn id="2" xr3:uid="{B5BEF9FE-D7B8-4290-AEE0-E0EC4EC8823E}" name="Сумма" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{B5BEF9FE-D7B8-4290-AEE0-E0EC4EC8823E}" name="Сумма" dataDxfId="11">
       <calculatedColumnFormula>E1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{63DD5922-AB67-4841-BF05-2F18A4E077CE}" name="Вложенная сумма"/>
-    <tableColumn id="4" xr3:uid="{E2A90522-B5EA-47C9-9FB4-90963699F3A8}" name="Процент в конце" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{E2A90522-B5EA-47C9-9FB4-90963699F3A8}" name="Процент в конце" dataDxfId="10">
       <calculatedColumnFormula>(0.07/12)*(B2+C2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4DB15378-9822-4AD5-951A-A9098578BAB0}" name="Сумма в конце" dataDxfId="5">
+    <tableColumn id="5" xr3:uid="{4DB15378-9822-4AD5-951A-A9098578BAB0}" name="Сумма в конце" dataDxfId="9">
       <calculatedColumnFormula>D2+B2+C2-Table3[[#This Row],[Снятие]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3A29E300-0E6C-456A-B93B-BC5C5A093CC8}" name="Снятие" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{0B586C98-591F-4D6B-96EE-21C53301CCD8}" name="Года" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{3E4E1630-0973-4B81-AC9B-DA92E19E7CAE}" name="Предпологаемая моя зп" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{3A29E300-0E6C-456A-B93B-BC5C5A093CC8}" name="Снятие" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{0B586C98-591F-4D6B-96EE-21C53301CCD8}" name="Года" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{3E4E1630-0973-4B81-AC9B-DA92E19E7CAE}" name="Предпологаемая моя зп" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B82F170B-19B7-421D-AC39-71A69FFA708D}" name="Table1" displayName="Table1" ref="A1:F870" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B82F170B-19B7-421D-AC39-71A69FFA708D}" name="Table1" displayName="Table1" ref="A1:F870" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:F870" xr:uid="{B82F170B-19B7-421D-AC39-71A69FFA708D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8CAEADE9-253F-4CBE-B551-6478CB6B3D9A}" name="Дата" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{4D79D684-C69A-4CC9-B8CD-CFF6C9D20347}" name="Остаток на начало дня" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{8CAEADE9-253F-4CBE-B551-6478CB6B3D9A}" name="Дата" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{4D79D684-C69A-4CC9-B8CD-CFF6C9D20347}" name="Остаток на начало дня" dataDxfId="3">
       <calculatedColumnFormula>F1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{AB992507-1FC0-4B8A-BA33-5F3DEAF35758}" name="Дневная ставка"/>
-    <tableColumn id="4" xr3:uid="{9B942243-90A7-4FA3-8436-41ED9C649A43}" name="Проценты за день" dataDxfId="8">
+    <tableColumn id="4" xr3:uid="{9B942243-90A7-4FA3-8436-41ED9C649A43}" name="Проценты за день" dataDxfId="2">
       <calculatedColumnFormula>B2*Table1[[#This Row],[Дневная ставка]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{D0EEC455-5371-434E-B324-95FE3351D14D}" name="Платёж"/>
-    <tableColumn id="6" xr3:uid="{A4C6051D-DA04-44FC-AD95-E0A849EC83F0}" name="Остаток на конец дня" dataDxfId="10">
+    <tableColumn id="6" xr3:uid="{A4C6051D-DA04-44FC-AD95-E0A849EC83F0}" name="Остаток на конец дня" dataDxfId="1">
       <calculatedColumnFormula>B2+D2-E2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -495,7 +495,7 @@
     <tableColumn id="5" xr3:uid="{446F6F4C-B5AD-4FD2-8384-9C374524EE26}" name="Остаточная сумма">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{028028A6-EC01-4B26-8059-51C0A7CBB59E}" name="Остаточная сумма по банку" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{028028A6-EC01-4B26-8059-51C0A7CBB59E}" name="Остаточная сумма по банку" dataDxfId="0">
       <calculatedColumnFormula>Table4[[#This Row],[Сумма]]-Table4[[#This Row],[Оплата по банку]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="B3">
         <f>SUM($L$2:$L$10)</f>
-        <v>3846</v>
+        <v>3346</v>
       </c>
       <c r="C3">
         <f>Table2[[#This Row],[Сумма]]-Table7[[#This Row],[Сумма]]</f>
-        <v>304</v>
+        <v>804</v>
       </c>
       <c r="K3" t="s">
         <v>54</v>
@@ -1366,11 +1366,11 @@
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B7" si="0">SUM($L$2:$L$10)</f>
-        <v>3846</v>
+        <v>3346</v>
       </c>
       <c r="C4">
         <f>Table2[[#This Row],[Сумма]]-Table7[[#This Row],[Сумма]]</f>
-        <v>304</v>
+        <v>804</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>3846</v>
+        <v>3346</v>
       </c>
       <c r="C5">
         <f>Table2[[#This Row],[Сумма]]-Table7[[#This Row],[Сумма]]</f>
-        <v>304</v>
+        <v>804</v>
       </c>
       <c r="K5" t="s">
         <v>56</v>
       </c>
       <c r="L5">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N5" t="s">
         <v>56</v>
@@ -1416,11 +1416,11 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>3846</v>
+        <v>3346</v>
       </c>
       <c r="C6">
         <f>Table2[[#This Row],[Сумма]]-Table7[[#This Row],[Сумма]]</f>
-        <v>304</v>
+        <v>804</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
@@ -1441,11 +1441,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>3846</v>
+        <v>3346</v>
       </c>
       <c r="C7">
         <f>Table2[[#This Row],[Сумма]]-Table7[[#This Row],[Сумма]]</f>
-        <v>304</v>
+        <v>804</v>
       </c>
       <c r="K7" t="s">
         <v>58</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="L11" s="5">
         <f>SUM(L2:L10)</f>
-        <v>3846</v>
+        <v>3346</v>
       </c>
       <c r="N11" t="s">
         <v>54</v>
@@ -1649,14 +1649,14 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>2000</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <f>(0.07/12)*(B2+C2)</f>
+        <f t="shared" ref="D2:D65" si="0">(0.07/12)*(B2+C2)</f>
         <v>11.666666666666668</v>
       </c>
       <c r="E2" s="1">
@@ -1677,19 +1677,19 @@
         <f>E2</f>
         <v>2011.6666666666667</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1500</v>
       </c>
       <c r="D3" s="1">
-        <f>(0.07/12)*(B3+C3)</f>
+        <f t="shared" si="0"/>
         <v>20.484722222222224</v>
       </c>
       <c r="E3" s="1">
-        <f>D3+B3+C3-Table3[[#This Row],[Снятие]]</f>
-        <v>3532.151388888889</v>
+        <f>B3+C3+D3-F3</f>
+        <v>500.00138888888932</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>3032.15</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1700,18 +1700,18 @@
       </c>
       <c r="B4" s="1">
         <f>E3</f>
-        <v>3532.151388888889</v>
-      </c>
-      <c r="C4">
-        <v>2000</v>
+        <v>500.00138888888932</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1500</v>
       </c>
       <c r="D4" s="1">
-        <f>(0.07/12)*(B4+C4)</f>
-        <v>32.270883101851858</v>
+        <f t="shared" si="0"/>
+        <v>11.666674768518522</v>
       </c>
       <c r="E4" s="1">
-        <f>D4+B4+C4-Table3[[#This Row],[Снятие]]</f>
-        <v>5564.4222719907411</v>
+        <f t="shared" ref="E4:E67" si="1">B4+C4+D4-F4</f>
+        <v>2011.6680636574079</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1724,19 +1724,19 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <f>E4</f>
-        <v>5564.4222719907411</v>
-      </c>
-      <c r="C5">
-        <v>6000</v>
+        <f t="shared" ref="B5:B68" si="2">E4</f>
+        <v>2011.6680636574079</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6500</v>
       </c>
       <c r="D5" s="1">
-        <f>(0.07/12)*(B5+C5)</f>
-        <v>67.459129919945994</v>
+        <f t="shared" si="0"/>
+        <v>49.651397038001548</v>
       </c>
       <c r="E5" s="1">
-        <f>D5+B5+C5-Table3[[#This Row],[Снятие]]</f>
-        <v>11631.881401910687</v>
+        <f t="shared" si="1"/>
+        <v>8561.3194606954094</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1751,22 +1751,22 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <f>E5</f>
-        <v>11631.881401910687</v>
-      </c>
-      <c r="C6">
-        <v>2200</v>
+        <f t="shared" si="2"/>
+        <v>8561.3194606954094</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1500</v>
       </c>
       <c r="D6" s="1">
-        <f>(0.07/12)*(B6+C6)</f>
-        <v>80.685974844479006</v>
+        <f t="shared" si="0"/>
+        <v>58.691030187389892</v>
       </c>
       <c r="E6" s="1">
-        <f>D6+B6+C6-Table3[[#This Row],[Снятие]]</f>
-        <v>10912.567376755165</v>
-      </c>
-      <c r="F6">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>10120.0104908828</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1776,22 +1776,22 @@
         <v>16</v>
       </c>
       <c r="B7" s="1">
-        <f>E6</f>
-        <v>10912.567376755165</v>
-      </c>
-      <c r="C7">
-        <v>1700</v>
+        <f t="shared" si="2"/>
+        <v>10120.0104908828</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1500</v>
       </c>
       <c r="D7" s="1">
-        <f>(0.07/12)*(B7+C7)</f>
-        <v>73.573309697738466</v>
+        <f t="shared" si="0"/>
+        <v>67.783394530149664</v>
       </c>
       <c r="E7" s="1">
-        <f>D7+B7+C7-Table3[[#This Row],[Снятие]]</f>
-        <v>1686.1406864529035</v>
-      </c>
-      <c r="F7">
-        <v>11000</v>
+        <f t="shared" si="1"/>
+        <v>1567.7838854129495</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10120.01</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1801,19 +1801,19 @@
         <v>17</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" ref="B8:B13" si="0">E7</f>
-        <v>1686.1406864529035</v>
-      </c>
-      <c r="C8">
-        <v>1700</v>
+        <f t="shared" si="2"/>
+        <v>1567.7838854129495</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1500</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" ref="D8:D13" si="1">(0.07/12)*(B8+C8)</f>
-        <v>19.752487337641938</v>
+        <f t="shared" si="0"/>
+        <v>17.895405998242207</v>
       </c>
       <c r="E8" s="1">
-        <f>D8+B8+C8-Table3[[#This Row],[Снятие]]</f>
-        <v>3405.8931737905455</v>
+        <f t="shared" si="1"/>
+        <v>3085.6792914111916</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1826,22 +1826,22 @@
         <v>18</v>
       </c>
       <c r="B9" s="1">
+        <f t="shared" si="2"/>
+        <v>3085.6792914111916</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>3405.8931737905455</v>
-      </c>
-      <c r="C9">
-        <v>1700</v>
-      </c>
-      <c r="D9" s="1">
+        <v>26.74979586656529</v>
+      </c>
+      <c r="E9" s="1">
         <f t="shared" si="1"/>
-        <v>29.78437684711152</v>
-      </c>
-      <c r="E9" s="1">
-        <f>D9+B9+C9-Table3[[#This Row],[Снятие]]</f>
-        <v>2135.6775506376571</v>
-      </c>
-      <c r="F9">
-        <v>3000</v>
+        <v>4612.4290872777574</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1851,19 +1851,19 @@
         <v>19</v>
       </c>
       <c r="B10" s="1">
+        <f t="shared" si="2"/>
+        <v>4612.4290872777574</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>2135.6775506376571</v>
-      </c>
-      <c r="C10">
-        <v>1700</v>
-      </c>
-      <c r="D10" s="1">
+        <v>35.65583634245359</v>
+      </c>
+      <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>22.374785712053001</v>
-      </c>
-      <c r="E10" s="1">
-        <f>D10+B10+C10-Table3[[#This Row],[Снятие]]</f>
-        <v>3858.05233634971</v>
+        <v>6148.0849236202112</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1876,19 +1876,19 @@
         <v>20</v>
       </c>
       <c r="B11" s="1">
+        <f t="shared" si="2"/>
+        <v>6148.0849236202112</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>3858.05233634971</v>
-      </c>
-      <c r="C11">
-        <v>1700</v>
-      </c>
-      <c r="D11" s="1">
+        <v>44.613828721117898</v>
+      </c>
+      <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>32.421971962039976</v>
-      </c>
-      <c r="E11" s="1">
-        <f>D11+B11+C11-Table3[[#This Row],[Снятие]]</f>
-        <v>5590.4743083117501</v>
+        <v>7692.6987523413291</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1901,22 +1901,22 @@
         <v>21</v>
       </c>
       <c r="B12" s="1">
+        <f t="shared" si="2"/>
+        <v>7692.6987523413291</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>5590.4743083117501</v>
-      </c>
-      <c r="C12">
-        <v>1700</v>
-      </c>
-      <c r="D12" s="1">
+        <v>53.62407605532443</v>
+      </c>
+      <c r="E12" s="1">
         <f t="shared" si="1"/>
-        <v>42.52776679848521</v>
-      </c>
-      <c r="E12" s="1">
-        <f>D12+B12+C12-Table3[[#This Row],[Снятие]]</f>
-        <v>2333.0020751102356</v>
-      </c>
-      <c r="F12">
-        <v>5000</v>
+        <v>9246.3228283966546</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1926,19 +1926,19 @@
         <v>22</v>
       </c>
       <c r="B13" s="1">
+        <f t="shared" si="2"/>
+        <v>9246.3228283966546</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>2333.0020751102356</v>
-      </c>
-      <c r="C13">
-        <v>1700</v>
-      </c>
-      <c r="D13" s="1">
+        <v>62.686883165647153</v>
+      </c>
+      <c r="E13" s="1">
         <f t="shared" si="1"/>
-        <v>23.525845438143044</v>
-      </c>
-      <c r="E13" s="1">
-        <f>D13+B13+C13-Table3[[#This Row],[Снятие]]</f>
-        <v>4056.5279205483785</v>
+        <v>10809.009711562301</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1951,19 +1951,19 @@
         <v>30</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" ref="B14:B25" si="2">E13</f>
-        <v>4056.5279205483785</v>
-      </c>
-      <c r="C14">
-        <v>1700</v>
+        <f t="shared" si="2"/>
+        <v>10809.009711562301</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1500</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" ref="D14:D25" si="3">(0.07/12)*(B14+C14)</f>
-        <v>33.579746203198873</v>
+        <f t="shared" si="0"/>
+        <v>71.80255665078009</v>
       </c>
       <c r="E14" s="1">
-        <f>D14+B14+C14-Table3[[#This Row],[Снятие]]</f>
-        <v>5790.1076667515772</v>
+        <f t="shared" si="1"/>
+        <v>12380.812268213082</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1977,18 +1977,18 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="2"/>
-        <v>5790.1076667515772</v>
-      </c>
-      <c r="C15">
-        <v>1700</v>
+        <v>12380.812268213082</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1500</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="3"/>
-        <v>43.692294722717534</v>
+        <f t="shared" si="0"/>
+        <v>80.97140489790965</v>
       </c>
       <c r="E15" s="1">
-        <f>D15+B15+C15-Table3[[#This Row],[Снятие]]</f>
-        <v>7533.7999614742948</v>
+        <f t="shared" si="1"/>
+        <v>13961.783673110991</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2002,18 +2002,18 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="2"/>
-        <v>7533.7999614742948</v>
-      </c>
-      <c r="C16">
-        <v>1700</v>
+        <v>13961.783673110991</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1500</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="3"/>
-        <v>53.863833108600055</v>
+        <f t="shared" si="0"/>
+        <v>90.193738093147445</v>
       </c>
       <c r="E16" s="1">
-        <f>D16+B16+C16-Table3[[#This Row],[Снятие]]</f>
-        <v>9287.6637945828952</v>
+        <f t="shared" si="1"/>
+        <v>15551.977411204138</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2027,18 +2027,18 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="2"/>
-        <v>9287.6637945828952</v>
-      </c>
-      <c r="C17">
-        <v>7525</v>
+        <v>15551.977411204138</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1500</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="3"/>
-        <v>98.073872135066892</v>
+        <f t="shared" si="0"/>
+        <v>99.46986823202414</v>
       </c>
       <c r="E17" s="1">
-        <f>D17+B17+C17-Table3[[#This Row],[Снятие]]</f>
-        <v>16910.737666717963</v>
+        <f t="shared" si="1"/>
+        <v>17151.447279436161</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2054,18 +2054,18 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="2"/>
-        <v>16910.737666717963</v>
-      </c>
-      <c r="C18">
-        <v>1900</v>
+        <v>17151.447279436161</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1500</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="3"/>
-        <v>109.72930305585479</v>
+        <f t="shared" si="0"/>
+        <v>108.80010913004428</v>
       </c>
       <c r="E18" s="1">
-        <f>D18+B18+C18-Table3[[#This Row],[Снятие]]</f>
-        <v>18920.466969773817</v>
+        <f t="shared" si="1"/>
+        <v>18760.247388566204</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2079,18 +2079,18 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="2"/>
-        <v>18920.466969773817</v>
-      </c>
-      <c r="C19">
-        <v>1900</v>
+        <v>18760.247388566204</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1500</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="3"/>
-        <v>121.45272399034727</v>
+        <f t="shared" si="0"/>
+        <v>118.18477643330286</v>
       </c>
       <c r="E19" s="1">
-        <f>D19+B19+C19-Table3[[#This Row],[Снятие]]</f>
-        <v>20941.919693764165</v>
+        <f t="shared" si="1"/>
+        <v>20378.432164999507</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2104,18 +2104,18 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="2"/>
-        <v>20941.919693764165</v>
-      </c>
-      <c r="C20">
-        <v>1900</v>
+        <v>20378.432164999507</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1500</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="3"/>
-        <v>133.24453154695763</v>
+        <f t="shared" si="0"/>
+        <v>127.6241876291638</v>
       </c>
       <c r="E20" s="1">
-        <f>D20+B20+C20-Table3[[#This Row],[Снятие]]</f>
-        <v>22975.16422531112</v>
+        <f t="shared" si="1"/>
+        <v>22006.056352628671</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2129,18 +2129,18 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="2"/>
-        <v>22975.16422531112</v>
-      </c>
-      <c r="C21">
-        <v>1900</v>
+        <v>22006.056352628671</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1500</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="3"/>
-        <v>145.10512464764821</v>
+        <f t="shared" si="0"/>
+        <v>137.11866205700059</v>
       </c>
       <c r="E21" s="1">
-        <f>D21+B21+C21-Table3[[#This Row],[Снятие]]</f>
-        <v>25020.269349958769</v>
+        <f t="shared" si="1"/>
+        <v>23643.175014685672</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2154,18 +2154,18 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="2"/>
-        <v>25020.269349958769</v>
-      </c>
-      <c r="C22">
-        <v>1900</v>
+        <v>23643.175014685672</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1500</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="3"/>
-        <v>157.03490454142616</v>
+        <f t="shared" si="0"/>
+        <v>146.66852091899975</v>
       </c>
       <c r="E22" s="1">
-        <f>D22+B22+C22-Table3[[#This Row],[Снятие]]</f>
-        <v>27077.304254500195</v>
+        <f t="shared" si="1"/>
+        <v>25289.843535604672</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2179,18 +2179,18 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="2"/>
-        <v>27077.304254500195</v>
-      </c>
-      <c r="C23">
-        <v>1900</v>
+        <v>25289.843535604672</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1500</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="3"/>
-        <v>169.0342748179178</v>
+        <f t="shared" si="0"/>
+        <v>156.27408729102726</v>
       </c>
       <c r="E23" s="1">
-        <f>D23+B23+C23-Table3[[#This Row],[Снятие]]</f>
-        <v>29146.338529318113</v>
+        <f t="shared" si="1"/>
+        <v>26946.117622895701</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2204,18 +2204,18 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="2"/>
-        <v>29146.338529318113</v>
-      </c>
-      <c r="C24">
-        <v>1900</v>
+        <v>26946.117622895701</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1500</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="3"/>
-        <v>181.10364142102233</v>
+        <f t="shared" si="0"/>
+        <v>165.93568613355828</v>
       </c>
       <c r="E24" s="1">
-        <f>D24+B24+C24-Table3[[#This Row],[Снятие]]</f>
-        <v>31227.442170739134</v>
+        <f t="shared" si="1"/>
+        <v>28612.053309029259</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2229,18 +2229,18 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="2"/>
-        <v>31227.442170739134</v>
-      </c>
-      <c r="C25">
-        <v>1900</v>
+        <v>28612.053309029259</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1500</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" si="3"/>
-        <v>193.24341266264494</v>
+        <f t="shared" si="0"/>
+        <v>175.6536443026707</v>
       </c>
       <c r="E25" s="1">
-        <f>D25+B25+C25-Table3[[#This Row],[Снятие]]</f>
-        <v>33320.685583401777</v>
+        <f t="shared" si="1"/>
+        <v>30287.70695333193</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2253,19 +2253,19 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" ref="B26:B37" si="4">E25</f>
-        <v>33320.685583401777</v>
-      </c>
-      <c r="C26">
-        <v>1900</v>
+        <f t="shared" si="2"/>
+        <v>30287.70695333193</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1500</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26:D37" si="5">(0.07/12)*(B26+C26)</f>
-        <v>205.45399923651038</v>
+        <f t="shared" si="0"/>
+        <v>185.42829056110293</v>
       </c>
       <c r="E26" s="1">
-        <f>D26+B26+C26-Table3[[#This Row],[Снятие]]</f>
-        <v>35426.139582638287</v>
+        <f t="shared" si="1"/>
+        <v>31973.135243893033</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2278,19 +2278,19 @@
         <v>12</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="4"/>
-        <v>35426.139582638287</v>
-      </c>
-      <c r="C27">
-        <v>1900</v>
+        <f t="shared" si="2"/>
+        <v>31973.135243893033</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1500</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="5"/>
-        <v>217.7358142320567</v>
+        <f t="shared" si="0"/>
+        <v>195.25995558937603</v>
       </c>
       <c r="E27" s="1">
-        <f>D27+B27+C27-Table3[[#This Row],[Снятие]]</f>
-        <v>37543.875396870346</v>
+        <f t="shared" si="1"/>
+        <v>33668.395199482409</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2303,19 +2303,19 @@
         <v>13</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="4"/>
-        <v>37543.875396870346</v>
-      </c>
-      <c r="C28">
-        <v>1900</v>
+        <f t="shared" si="2"/>
+        <v>33668.395199482409</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1500</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="5"/>
-        <v>230.08927314841037</v>
+        <f t="shared" si="0"/>
+        <v>205.14897199698072</v>
       </c>
       <c r="E28" s="1">
-        <f>D28+B28+C28-Table3[[#This Row],[Снятие]]</f>
-        <v>39673.964670018759</v>
+        <f t="shared" si="1"/>
+        <v>35373.544171479392</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2328,19 +2328,19 @@
         <v>14</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" si="4"/>
-        <v>39673.964670018759</v>
-      </c>
-      <c r="C29">
-        <v>8025</v>
+        <f t="shared" si="2"/>
+        <v>35373.544171479392</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1500</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" si="5"/>
-        <v>278.24396057510944</v>
+        <f t="shared" si="0"/>
+        <v>215.0956743336298</v>
       </c>
       <c r="E29" s="1">
-        <f>D29+B29+C29-Table3[[#This Row],[Снятие]]</f>
-        <v>47977.208630593865</v>
+        <f t="shared" si="1"/>
+        <v>37088.639845813021</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2357,19 +2357,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="4"/>
-        <v>47977.208630593865</v>
-      </c>
-      <c r="C30">
-        <v>1900</v>
+        <f t="shared" si="2"/>
+        <v>37088.639845813021</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1500</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="5"/>
-        <v>290.95038367846422</v>
+        <f t="shared" si="0"/>
+        <v>225.10039910057597</v>
       </c>
       <c r="E30" s="1">
-        <f>D30+B30+C30-Table3[[#This Row],[Снятие]]</f>
-        <v>50168.159014272329</v>
+        <f t="shared" si="1"/>
+        <v>38813.740244913599</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2382,19 +2382,19 @@
         <v>16</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" si="4"/>
-        <v>50168.159014272329</v>
-      </c>
-      <c r="C31">
-        <v>1900</v>
+        <f t="shared" si="2"/>
+        <v>38813.740244913599</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1500</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="5"/>
-        <v>303.73092758325527</v>
+        <f t="shared" si="0"/>
+        <v>235.16348476199602</v>
       </c>
       <c r="E31" s="1">
-        <f>D31+B31+C31-Table3[[#This Row],[Снятие]]</f>
-        <v>52371.889941855581</v>
+        <f t="shared" si="1"/>
+        <v>40548.903729675592</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>17</v>
       </c>
       <c r="B32" s="1">
-        <f t="shared" si="4"/>
-        <v>52371.889941855581</v>
-      </c>
-      <c r="C32">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>40548.903729675592</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1500</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="5"/>
-        <v>320.37769132749088</v>
+        <f t="shared" si="0"/>
+        <v>245.28527175644098</v>
       </c>
       <c r="E32" s="1">
-        <f>D32+B32+C32-Table3[[#This Row],[Снятие]]</f>
-        <v>55242.267633183073</v>
+        <f t="shared" si="1"/>
+        <v>42294.189001432031</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2432,19 +2432,19 @@
         <v>18</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" si="4"/>
-        <v>55242.267633183073</v>
-      </c>
-      <c r="C33">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>42294.189001432031</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1500</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="5"/>
-        <v>337.12156119356797</v>
+        <f t="shared" si="0"/>
+        <v>255.46610250835352</v>
       </c>
       <c r="E33" s="1">
-        <f>D33+B33+C33-Table3[[#This Row],[Снятие]]</f>
-        <v>58129.389194376643</v>
+        <f t="shared" si="1"/>
+        <v>44049.655103940386</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2457,19 +2457,19 @@
         <v>19</v>
       </c>
       <c r="B34" s="1">
-        <f t="shared" si="4"/>
-        <v>58129.389194376643</v>
-      </c>
-      <c r="C34">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>44049.655103940386</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1500</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="5"/>
-        <v>353.96310363386374</v>
+        <f t="shared" si="0"/>
+        <v>265.70632143965224</v>
       </c>
       <c r="E34" s="1">
-        <f>D34+B34+C34-Table3[[#This Row],[Снятие]]</f>
-        <v>61033.352298010504</v>
+        <f t="shared" si="1"/>
+        <v>45815.361425380041</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2482,19 +2482,19 @@
         <v>20</v>
       </c>
       <c r="B35" s="1">
-        <f t="shared" si="4"/>
-        <v>61033.352298010504</v>
-      </c>
-      <c r="C35">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>45815.361425380041</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1500</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="5"/>
-        <v>370.90288840506128</v>
+        <f t="shared" si="0"/>
+        <v>276.00627498138357</v>
       </c>
       <c r="E35" s="1">
-        <f>D35+B35+C35-Table3[[#This Row],[Снятие]]</f>
-        <v>63954.255186415568</v>
+        <f t="shared" si="1"/>
+        <v>47591.367700361421</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2507,19 +2507,19 @@
         <v>21</v>
       </c>
       <c r="B36" s="1">
-        <f t="shared" si="4"/>
-        <v>63954.255186415568</v>
-      </c>
-      <c r="C36">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>47591.367700361421</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1500</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="5"/>
-        <v>387.94148858742415</v>
+        <f t="shared" si="0"/>
+        <v>286.36631158544162</v>
       </c>
       <c r="E36" s="1">
-        <f>D36+B36+C36-Table3[[#This Row],[Снятие]]</f>
-        <v>66892.196675002982</v>
+        <f t="shared" si="1"/>
+        <v>49377.734011946864</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2532,19 +2532,19 @@
         <v>22</v>
       </c>
       <c r="B37" s="1">
-        <f t="shared" si="4"/>
-        <v>66892.196675002982</v>
-      </c>
-      <c r="C37">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>49377.734011946864</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1500</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="5"/>
-        <v>405.07948060418408</v>
+        <f t="shared" si="0"/>
+        <v>296.78678173635672</v>
       </c>
       <c r="E37" s="1">
-        <f>D37+B37+C37-Table3[[#This Row],[Снятие]]</f>
-        <v>69847.276155607164</v>
+        <f t="shared" si="1"/>
+        <v>51174.520793683223</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2557,19 +2557,19 @@
         <v>32</v>
       </c>
       <c r="B38" s="1">
-        <f t="shared" ref="B38:B49" si="6">E37</f>
-        <v>69847.276155607164</v>
-      </c>
-      <c r="C38">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>51174.520793683223</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1500</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" ref="D38:D49" si="7">(0.07/12)*(B38+C38)</f>
-        <v>422.31744424104181</v>
+        <f t="shared" si="0"/>
+        <v>307.26803796315215</v>
       </c>
       <c r="E38" s="1">
-        <f>D38+B38+C38-Table3[[#This Row],[Снятие]]</f>
-        <v>72819.593599848202</v>
+        <f t="shared" si="1"/>
+        <v>52981.788831646372</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2582,19 +2582,19 @@
         <v>12</v>
       </c>
       <c r="B39" s="1">
-        <f t="shared" si="6"/>
-        <v>72819.593599848202</v>
-      </c>
-      <c r="C39">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>52981.788831646372</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1500</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="7"/>
-        <v>439.6559626657812</v>
+        <f t="shared" si="0"/>
+        <v>317.81043485127054</v>
       </c>
       <c r="E39" s="1">
-        <f>D39+B39+C39-Table3[[#This Row],[Снятие]]</f>
-        <v>75809.249562513985</v>
+        <f t="shared" si="1"/>
+        <v>54799.599266497644</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2607,19 +2607,19 @@
         <v>13</v>
       </c>
       <c r="B40" s="1">
-        <f t="shared" si="6"/>
-        <v>75809.249562513985</v>
-      </c>
-      <c r="C40">
-        <v>2550</v>
+        <f t="shared" si="2"/>
+        <v>54799.599266497644</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1500</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="7"/>
-        <v>457.09562244799827</v>
+        <f t="shared" si="0"/>
+        <v>328.41432905456958</v>
       </c>
       <c r="E40" s="1">
-        <f>D40+B40+C40-Table3[[#This Row],[Снятие]]</f>
-        <v>78816.345184961989</v>
+        <f t="shared" si="1"/>
+        <v>56628.013595552213</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2632,19 +2632,19 @@
         <v>14</v>
       </c>
       <c r="B41" s="1">
-        <f t="shared" si="6"/>
-        <v>78816.345184961989</v>
-      </c>
-      <c r="C41">
-        <v>9375</v>
+        <f t="shared" si="2"/>
+        <v>56628.013595552213</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1500</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="7"/>
-        <v>514.4495135789449</v>
+        <f t="shared" si="0"/>
+        <v>339.0800793073879</v>
       </c>
       <c r="E41" s="1">
-        <f>D41+B41+C41-Table3[[#This Row],[Снятие]]</f>
-        <v>88705.794698540936</v>
+        <f t="shared" si="1"/>
+        <v>58467.0936748596</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2661,19 +2661,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="1">
-        <f t="shared" si="6"/>
-        <v>88705.794698540936</v>
-      </c>
-      <c r="C42">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>58467.0936748596</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1500</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="7"/>
-        <v>533.49213574148882</v>
+        <f t="shared" si="0"/>
+        <v>349.80804643668102</v>
       </c>
       <c r="E42" s="1">
-        <f>D42+B42+C42-Table3[[#This Row],[Снятие]]</f>
-        <v>91989.286834282422</v>
+        <f t="shared" si="1"/>
+        <v>60316.901721296279</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2686,19 +2686,19 @@
         <v>16</v>
       </c>
       <c r="B43" s="1">
-        <f t="shared" si="6"/>
-        <v>91989.286834282422</v>
-      </c>
-      <c r="C43">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>60316.901721296279</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1500</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="7"/>
-        <v>552.64583986664752</v>
+        <f t="shared" si="0"/>
+        <v>360.5985933742283</v>
       </c>
       <c r="E43" s="1">
-        <f>D43+B43+C43-Table3[[#This Row],[Снятие]]</f>
-        <v>95291.932674149066</v>
+        <f t="shared" si="1"/>
+        <v>62177.500314670506</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2711,19 +2711,19 @@
         <v>17</v>
       </c>
       <c r="B44" s="1">
-        <f t="shared" si="6"/>
-        <v>95291.932674149066</v>
-      </c>
-      <c r="C44">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>62177.500314670506</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1500</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="7"/>
-        <v>571.91127393253623</v>
+        <f t="shared" si="0"/>
+        <v>371.45208516891131</v>
       </c>
       <c r="E44" s="1">
-        <f>D44+B44+C44-Table3[[#This Row],[Снятие]]</f>
-        <v>98613.843948081601</v>
+        <f t="shared" si="1"/>
+        <v>64048.952399839414</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2736,19 +2736,19 @@
         <v>18</v>
       </c>
       <c r="B45" s="1">
-        <f t="shared" si="6"/>
-        <v>98613.843948081601</v>
-      </c>
-      <c r="C45">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>64048.952399839414</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1500</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="7"/>
-        <v>591.28908969714269</v>
+        <f t="shared" si="0"/>
+        <v>382.36888899906324</v>
       </c>
       <c r="E45" s="1">
-        <f>D45+B45+C45-Table3[[#This Row],[Снятие]]</f>
-        <v>101955.13303777874</v>
+        <f t="shared" si="1"/>
+        <v>65931.321288838473</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2761,19 +2761,19 @@
         <v>19</v>
       </c>
       <c r="B46" s="1">
-        <f t="shared" si="6"/>
-        <v>101955.13303777874</v>
-      </c>
-      <c r="C46">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>65931.321288838473</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1500</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" si="7"/>
-        <v>610.77994272037597</v>
+        <f t="shared" si="0"/>
+        <v>393.34937418489113</v>
       </c>
       <c r="E46" s="1">
-        <f>D46+B46+C46-Table3[[#This Row],[Снятие]]</f>
-        <v>105315.91298049911</v>
+        <f t="shared" si="1"/>
+        <v>67824.670663023368</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -2786,19 +2786,19 @@
         <v>20</v>
       </c>
       <c r="B47" s="1">
-        <f t="shared" si="6"/>
-        <v>105315.91298049911</v>
-      </c>
-      <c r="C47">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>67824.670663023368</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1500</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="7"/>
-        <v>630.3844923862448</v>
+        <f t="shared" si="0"/>
+        <v>404.39391220096968</v>
       </c>
       <c r="E47" s="1">
-        <f>D47+B47+C47-Table3[[#This Row],[Снятие]]</f>
-        <v>108696.29747288536</v>
+        <f t="shared" si="1"/>
+        <v>69729.064575224344</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -2811,19 +2811,19 @@
         <v>21</v>
       </c>
       <c r="B48" s="1">
-        <f t="shared" si="6"/>
-        <v>108696.29747288536</v>
-      </c>
-      <c r="C48">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>69729.064575224344</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1500</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" si="7"/>
-        <v>650.10340192516458</v>
+        <f t="shared" si="0"/>
+        <v>415.50287668880867</v>
       </c>
       <c r="E48" s="1">
-        <f>D48+B48+C48-Table3[[#This Row],[Снятие]]</f>
-        <v>112096.40087481053</v>
+        <f t="shared" si="1"/>
+        <v>71644.567451913157</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -2836,19 +2836,19 @@
         <v>22</v>
       </c>
       <c r="B49" s="1">
-        <f t="shared" si="6"/>
-        <v>112096.40087481053</v>
-      </c>
-      <c r="C49">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>71644.567451913157</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1500</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" si="7"/>
-        <v>669.93733843639473</v>
+        <f t="shared" si="0"/>
+        <v>426.67664346949346</v>
       </c>
       <c r="E49" s="1">
-        <f>D49+B49+C49-Table3[[#This Row],[Снятие]]</f>
-        <v>115516.33821324693</v>
+        <f t="shared" si="1"/>
+        <v>73571.244095382644</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -2861,19 +2861,19 @@
         <v>33</v>
       </c>
       <c r="B50" s="1">
-        <f t="shared" ref="B50:B61" si="8">E49</f>
-        <v>115516.33821324693</v>
-      </c>
-      <c r="C50">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>73571.244095382644</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1500</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" ref="D50:D61" si="9">(0.07/12)*(B50+C50)</f>
-        <v>689.88697291060714</v>
+        <f t="shared" si="0"/>
+        <v>437.9155905563988</v>
       </c>
       <c r="E50" s="1">
-        <f>D50+B50+C50-Table3[[#This Row],[Снятие]]</f>
-        <v>118956.22518615754</v>
+        <f t="shared" si="1"/>
+        <v>75509.159685939041</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -2886,19 +2886,19 @@
         <v>12</v>
       </c>
       <c r="B51" s="1">
-        <f t="shared" si="8"/>
-        <v>118956.22518615754</v>
-      </c>
-      <c r="C51">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>75509.159685939041</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1500</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" si="9"/>
-        <v>709.95298025258569</v>
+        <f t="shared" si="0"/>
+        <v>449.22009816797777</v>
       </c>
       <c r="E51" s="1">
-        <f>D51+B51+C51-Table3[[#This Row],[Снятие]]</f>
-        <v>122416.17816641011</v>
+        <f t="shared" si="1"/>
+        <v>77458.379784107019</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -2911,19 +2911,19 @@
         <v>13</v>
       </c>
       <c r="B52" s="1">
-        <f t="shared" si="8"/>
-        <v>122416.17816641011</v>
-      </c>
-      <c r="C52">
-        <v>2750</v>
+        <f t="shared" si="2"/>
+        <v>77458.379784107019</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1500</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="9"/>
-        <v>730.13603930405907</v>
+        <f t="shared" si="0"/>
+        <v>460.59054874062429</v>
       </c>
       <c r="E52" s="1">
-        <f>D52+B52+C52-Table3[[#This Row],[Снятие]]</f>
-        <v>125896.31420571417</v>
+        <f t="shared" si="1"/>
+        <v>79418.970332847646</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -2936,19 +2936,19 @@
         <v>14</v>
       </c>
       <c r="B53" s="1">
-        <f t="shared" si="8"/>
-        <v>125896.31420571417</v>
-      </c>
-      <c r="C53">
-        <v>10075</v>
+        <f t="shared" si="2"/>
+        <v>79418.970332847646</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1500</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" si="9"/>
-        <v>793.16599953333264</v>
+        <f t="shared" si="0"/>
+        <v>472.02732694161131</v>
       </c>
       <c r="E53" s="1">
-        <f>D53+B53+C53-Table3[[#This Row],[Снятие]]</f>
-        <v>136764.4802052475</v>
+        <f t="shared" si="1"/>
+        <v>81390.997659789253</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -2965,19 +2965,19 @@
         <v>15</v>
       </c>
       <c r="B54" s="1">
-        <f t="shared" si="8"/>
-        <v>136764.4802052475</v>
-      </c>
-      <c r="C54">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>81390.997659789253</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1500</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="9"/>
-        <v>815.00113453061044</v>
+        <f t="shared" si="0"/>
+        <v>483.53081968210398</v>
       </c>
       <c r="E54" s="1">
-        <f>D54+B54+C54-Table3[[#This Row],[Снятие]]</f>
-        <v>140529.48133977811</v>
+        <f t="shared" si="1"/>
+        <v>83374.528479471352</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -2990,19 +2990,19 @@
         <v>16</v>
       </c>
       <c r="B55" s="1">
-        <f t="shared" si="8"/>
-        <v>140529.48133977811</v>
-      </c>
-      <c r="C55">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>83374.528479471352</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1500</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="9"/>
-        <v>836.96364114870573</v>
+        <f t="shared" si="0"/>
+        <v>495.10141613024956</v>
       </c>
       <c r="E55" s="1">
-        <f>D55+B55+C55-Table3[[#This Row],[Снятие]]</f>
-        <v>144316.44498092681</v>
+        <f t="shared" si="1"/>
+        <v>85369.629895601596</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3015,19 +3015,19 @@
         <v>17</v>
       </c>
       <c r="B56" s="1">
-        <f t="shared" si="8"/>
-        <v>144316.44498092681</v>
-      </c>
-      <c r="C56">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>85369.629895601596</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1500</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" si="9"/>
-        <v>859.05426238873974</v>
+        <f t="shared" si="0"/>
+        <v>506.73950772434267</v>
       </c>
       <c r="E56" s="1">
-        <f>D56+B56+C56-Table3[[#This Row],[Снятие]]</f>
-        <v>148125.49924331554</v>
+        <f t="shared" si="1"/>
+        <v>87376.369403325938</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3040,19 +3040,19 @@
         <v>18</v>
       </c>
       <c r="B57" s="1">
-        <f t="shared" si="8"/>
-        <v>148125.49924331554</v>
-      </c>
-      <c r="C57">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>87376.369403325938</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1500</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="9"/>
-        <v>881.27374558600741</v>
+        <f t="shared" si="0"/>
+        <v>518.44548818606802</v>
       </c>
       <c r="E57" s="1">
-        <f>D57+B57+C57-Table3[[#This Row],[Снятие]]</f>
-        <v>151956.77298890156</v>
+        <f t="shared" si="1"/>
+        <v>89394.814891512011</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3065,19 +3065,19 @@
         <v>19</v>
       </c>
       <c r="B58" s="1">
-        <f t="shared" si="8"/>
-        <v>151956.77298890156</v>
-      </c>
-      <c r="C58">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>89394.814891512011</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1500</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" si="9"/>
-        <v>903.62284243525914</v>
+        <f t="shared" si="0"/>
+        <v>530.21975353382004</v>
       </c>
       <c r="E58" s="1">
-        <f>D58+B58+C58-Table3[[#This Row],[Снятие]]</f>
-        <v>155810.39583133682</v>
+        <f t="shared" si="1"/>
+        <v>91425.034645045831</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3090,19 +3090,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="1">
-        <f t="shared" si="8"/>
-        <v>155810.39583133682</v>
-      </c>
-      <c r="C59">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>91425.034645045831</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1500</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="9"/>
-        <v>926.10230901613147</v>
+        <f t="shared" si="0"/>
+        <v>542.06270209610068</v>
       </c>
       <c r="E59" s="1">
-        <f>D59+B59+C59-Table3[[#This Row],[Снятие]]</f>
-        <v>159686.49814035295</v>
+        <f t="shared" si="1"/>
+        <v>93467.097347141927</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3115,19 +3115,19 @@
         <v>21</v>
       </c>
       <c r="B60" s="1">
-        <f t="shared" si="8"/>
-        <v>159686.49814035295</v>
-      </c>
-      <c r="C60">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>93467.097347141927</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1500</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="9"/>
-        <v>948.71290581872563</v>
+        <f t="shared" si="0"/>
+        <v>553.97473452499457</v>
       </c>
       <c r="E60" s="1">
-        <f>D60+B60+C60-Table3[[#This Row],[Снятие]]</f>
-        <v>163585.21104617167</v>
+        <f t="shared" si="1"/>
+        <v>95521.07208166692</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3140,19 +3140,19 @@
         <v>22</v>
       </c>
       <c r="B61" s="1">
-        <f t="shared" si="8"/>
-        <v>163585.21104617167</v>
-      </c>
-      <c r="C61">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>95521.07208166692</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1500</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" si="9"/>
-        <v>971.45539776933481</v>
+        <f t="shared" si="0"/>
+        <v>565.95625380972376</v>
       </c>
       <c r="E61" s="1">
-        <f>D61+B61+C61-Table3[[#This Row],[Снятие]]</f>
-        <v>167506.66644394101</v>
+        <f t="shared" si="1"/>
+        <v>97587.028335476643</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3165,19 +3165,19 @@
         <v>34</v>
       </c>
       <c r="B62" s="1">
-        <f t="shared" ref="B62:B73" si="10">E61</f>
-        <v>167506.66644394101</v>
-      </c>
-      <c r="C62">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>97587.028335476643</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1500</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" ref="D62:D73" si="11">(0.07/12)*(B62+C62)</f>
-        <v>994.33055425632256</v>
+        <f t="shared" si="0"/>
+        <v>578.00766529028044</v>
       </c>
       <c r="E62" s="1">
-        <f>D62+B62+C62-Table3[[#This Row],[Снятие]]</f>
-        <v>171450.99699819734</v>
+        <f t="shared" si="1"/>
+        <v>99665.036000766922</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3190,19 +3190,19 @@
         <v>12</v>
       </c>
       <c r="B63" s="1">
-        <f t="shared" si="10"/>
-        <v>171450.99699819734</v>
-      </c>
-      <c r="C63">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>99665.036000766922</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1500</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="11"/>
-        <v>1017.3391491561512</v>
+        <f t="shared" si="0"/>
+        <v>590.12937667114045</v>
       </c>
       <c r="E63" s="1">
-        <f>D63+B63+C63-Table3[[#This Row],[Снятие]]</f>
-        <v>175418.33614735349</v>
+        <f t="shared" si="1"/>
+        <v>101755.16537743807</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3215,19 +3215,19 @@
         <v>13</v>
       </c>
       <c r="B64" s="1">
-        <f t="shared" si="10"/>
-        <v>175418.33614735349</v>
-      </c>
-      <c r="C64">
-        <v>2950</v>
+        <f t="shared" si="2"/>
+        <v>101755.16537743807</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1500</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="11"/>
-        <v>1040.4819608595622</v>
+        <f t="shared" si="0"/>
+        <v>602.32179803505539</v>
       </c>
       <c r="E64" s="1">
-        <f>D64+B64+C64-Table3[[#This Row],[Снятие]]</f>
-        <v>179408.81810821305</v>
+        <f t="shared" si="1"/>
+        <v>103857.48717547313</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3240,19 +3240,19 @@
         <v>14</v>
       </c>
       <c r="B65" s="1">
-        <f t="shared" si="10"/>
-        <v>179408.81810821305</v>
-      </c>
-      <c r="C65">
-        <v>10775</v>
+        <f t="shared" si="2"/>
+        <v>103857.48717547313</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1500</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="11"/>
-        <v>1109.4056056312429</v>
+        <f t="shared" si="0"/>
+        <v>614.58534185692656</v>
       </c>
       <c r="E65" s="1">
-        <f>D65+B65+C65-Table3[[#This Row],[Снятие]]</f>
-        <v>191293.22371384429</v>
+        <f t="shared" si="1"/>
+        <v>105972.07251733006</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3269,19 +3269,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="1">
-        <f t="shared" si="10"/>
-        <v>191293.22371384429</v>
-      </c>
-      <c r="C66">
-        <v>3150</v>
+        <f t="shared" si="2"/>
+        <v>105972.07251733006</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1500</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="11"/>
-        <v>1134.2521383307585</v>
+        <f t="shared" ref="D66:D129" si="3">(0.07/12)*(B66+C66)</f>
+        <v>626.92042301775871</v>
       </c>
       <c r="E66" s="1">
-        <f>D66+B66+C66-Table3[[#This Row],[Снятие]]</f>
-        <v>195577.47585217503</v>
+        <f t="shared" si="1"/>
+        <v>108098.99294034782</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3294,19 +3294,19 @@
         <v>16</v>
       </c>
       <c r="B67" s="1">
-        <f t="shared" si="10"/>
-        <v>195577.47585217503</v>
-      </c>
-      <c r="C67">
-        <v>3150</v>
+        <f t="shared" si="2"/>
+        <v>108098.99294034782</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1500</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" si="11"/>
-        <v>1159.2436091376878</v>
+        <f t="shared" si="3"/>
+        <v>639.32745881869562</v>
       </c>
       <c r="E67" s="1">
-        <f>D67+B67+C67-Table3[[#This Row],[Снятие]]</f>
-        <v>199886.71946131272</v>
+        <f t="shared" si="1"/>
+        <v>110238.32039916651</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3319,19 +3319,19 @@
         <v>17</v>
       </c>
       <c r="B68" s="1">
-        <f t="shared" si="10"/>
-        <v>199886.71946131272</v>
-      </c>
-      <c r="C68">
-        <v>3150</v>
+        <f t="shared" si="2"/>
+        <v>110238.32039916651</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1500</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="11"/>
-        <v>1184.3808635243242</v>
+        <f t="shared" si="3"/>
+        <v>651.80686899513796</v>
       </c>
       <c r="E68" s="1">
-        <f>D68+B68+C68-Table3[[#This Row],[Снятие]]</f>
-        <v>204221.10032483705</v>
+        <f t="shared" ref="E68:E131" si="4">B68+C68+D68-F68</f>
+        <v>112390.12726816164</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3344,19 +3344,19 @@
         <v>18</v>
       </c>
       <c r="B69" s="1">
-        <f t="shared" si="10"/>
-        <v>204221.10032483705</v>
-      </c>
-      <c r="C69">
-        <v>3150</v>
+        <f t="shared" ref="B69:B132" si="5">E68</f>
+        <v>112390.12726816164</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1500</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="11"/>
-        <v>1209.6647518948828</v>
+        <f t="shared" si="3"/>
+        <v>664.35907573094289</v>
       </c>
       <c r="E69" s="1">
-        <f>D69+B69+C69-Table3[[#This Row],[Снятие]]</f>
-        <v>208580.76507673194</v>
+        <f t="shared" si="4"/>
+        <v>114554.48634389258</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3369,19 +3369,19 @@
         <v>19</v>
       </c>
       <c r="B70" s="1">
-        <f t="shared" si="10"/>
-        <v>208580.76507673194</v>
-      </c>
-      <c r="C70">
-        <v>3150</v>
+        <f t="shared" si="5"/>
+        <v>114554.48634389258</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1500</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="11"/>
-        <v>1235.0961296142698</v>
+        <f t="shared" si="3"/>
+        <v>676.98450367270675</v>
       </c>
       <c r="E70" s="1">
-        <f>D70+B70+C70-Table3[[#This Row],[Снятие]]</f>
-        <v>212965.86120634622</v>
+        <f t="shared" si="4"/>
+        <v>116731.47084756529</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3394,19 +3394,19 @@
         <v>20</v>
       </c>
       <c r="B71" s="1">
-        <f t="shared" si="10"/>
-        <v>212965.86120634622</v>
-      </c>
-      <c r="C71">
-        <v>3150</v>
+        <f t="shared" si="5"/>
+        <v>116731.47084756529</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1500</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="11"/>
-        <v>1260.6758570370196</v>
+        <f t="shared" si="3"/>
+        <v>689.68357994413088</v>
       </c>
       <c r="E71" s="1">
-        <f>D71+B71+C71-Table3[[#This Row],[Снятие]]</f>
-        <v>217376.53706338324</v>
+        <f t="shared" si="4"/>
+        <v>118921.15442750942</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3419,19 +3419,19 @@
         <v>21</v>
       </c>
       <c r="B72" s="1">
-        <f t="shared" si="10"/>
-        <v>217376.53706338324</v>
-      </c>
-      <c r="C72">
-        <v>3150</v>
+        <f t="shared" si="5"/>
+        <v>118921.15442750942</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1500</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="11"/>
-        <v>1286.4047995364022</v>
+        <f t="shared" si="3"/>
+        <v>702.45673416047168</v>
       </c>
       <c r="E72" s="1">
-        <f>D72+B72+C72-Table3[[#This Row],[Снятие]]</f>
-        <v>221812.94186291963</v>
+        <f t="shared" si="4"/>
+        <v>121123.61116166989</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3444,19 +3444,19 @@
         <v>22</v>
       </c>
       <c r="B73" s="1">
-        <f t="shared" si="10"/>
-        <v>221812.94186291963</v>
-      </c>
-      <c r="C73">
-        <v>3150</v>
+        <f t="shared" si="5"/>
+        <v>121123.61116166989</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1500</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="11"/>
-        <v>1312.2838275336978</v>
+        <f t="shared" si="3"/>
+        <v>715.30439844307443</v>
       </c>
       <c r="E73" s="1">
-        <f>D73+B73+C73-Table3[[#This Row],[Снятие]]</f>
-        <v>226275.22569045331</v>
+        <f t="shared" si="4"/>
+        <v>123338.91556011296</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>35</v>
       </c>
       <c r="B74" s="1">
-        <f t="shared" ref="B74:B85" si="12">E73</f>
-        <v>226275.22569045331</v>
-      </c>
-      <c r="C74">
-        <v>3150</v>
+        <f t="shared" si="5"/>
+        <v>123338.91556011296</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1500</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" ref="D74:D85" si="13">(0.07/12)*(B74+C74)</f>
-        <v>1338.3138165276443</v>
+        <f t="shared" si="3"/>
+        <v>728.2270074339923</v>
       </c>
       <c r="E74" s="1">
-        <f>D74+B74+C74-Table3[[#This Row],[Снятие]]</f>
-        <v>230763.53950698095</v>
+        <f t="shared" si="4"/>
+        <v>125567.14256754695</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3494,19 +3494,19 @@
         <v>12</v>
       </c>
       <c r="B75" s="1">
-        <f t="shared" si="12"/>
-        <v>230763.53950698095</v>
-      </c>
-      <c r="C75">
-        <v>3150</v>
+        <f t="shared" si="5"/>
+        <v>125567.14256754695</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1500</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="13"/>
-        <v>1364.4956471240555</v>
+        <f t="shared" si="3"/>
+        <v>741.22499831069058</v>
       </c>
       <c r="E75" s="1">
-        <f>D75+B75+C75-Table3[[#This Row],[Снятие]]</f>
-        <v>235278.03515410499</v>
+        <f t="shared" si="4"/>
+        <v>127808.36756585764</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3519,19 +3519,19 @@
         <v>13</v>
       </c>
       <c r="B76" s="1">
-        <f t="shared" si="12"/>
-        <v>235278.03515410499</v>
-      </c>
-      <c r="C76">
-        <v>3150</v>
+        <f t="shared" si="5"/>
+        <v>127808.36756585764</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1500</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="13"/>
-        <v>1390.8302050656125</v>
+        <f t="shared" si="3"/>
+        <v>754.29881080083624</v>
       </c>
       <c r="E76" s="1">
-        <f>D76+B76+C76-Table3[[#This Row],[Снятие]]</f>
-        <v>239818.8653591706</v>
+        <f t="shared" si="4"/>
+        <v>130062.66637665848</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -3544,19 +3544,19 @@
         <v>14</v>
       </c>
       <c r="B77" s="1">
-        <f t="shared" si="12"/>
-        <v>239818.8653591706</v>
-      </c>
-      <c r="C77">
-        <v>11475</v>
+        <f t="shared" si="5"/>
+        <v>130062.66637665848</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1500</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="13"/>
-        <v>1465.8808812618286</v>
+        <f t="shared" si="3"/>
+        <v>767.44888719717449</v>
       </c>
       <c r="E77" s="1">
-        <f>D77+B77+C77-Table3[[#This Row],[Снятие]]</f>
-        <v>252759.74624043243</v>
+        <f t="shared" si="4"/>
+        <v>132330.11526385567</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -3573,19 +3573,19 @@
         <v>15</v>
       </c>
       <c r="B78" s="1">
-        <f t="shared" si="12"/>
-        <v>252759.74624043243</v>
-      </c>
-      <c r="C78">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>132330.11526385567</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1500</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" si="13"/>
-        <v>1493.9735197358559</v>
+        <f t="shared" si="3"/>
+        <v>780.67567237249148</v>
       </c>
       <c r="E78" s="1">
-        <f>D78+B78+C78-Table3[[#This Row],[Снятие]]</f>
-        <v>257603.71976016829</v>
+        <f t="shared" si="4"/>
+        <v>134610.79093622815</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -3598,19 +3598,19 @@
         <v>16</v>
       </c>
       <c r="B79" s="1">
-        <f t="shared" si="12"/>
-        <v>257603.71976016829</v>
-      </c>
-      <c r="C79">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>134610.79093622815</v>
+      </c>
+      <c r="C79" s="1">
+        <v>1500</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="13"/>
-        <v>1522.2300319343151</v>
+        <f t="shared" si="3"/>
+        <v>793.97961379466426</v>
       </c>
       <c r="E79" s="1">
-        <f>D79+B79+C79-Table3[[#This Row],[Снятие]]</f>
-        <v>262475.94979210256</v>
+        <f t="shared" si="4"/>
+        <v>136904.7705500228</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -3623,19 +3623,19 @@
         <v>17</v>
       </c>
       <c r="B80" s="1">
-        <f t="shared" si="12"/>
-        <v>262475.94979210256</v>
-      </c>
-      <c r="C80">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>136904.7705500228</v>
+      </c>
+      <c r="C80" s="1">
+        <v>1500</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="13"/>
-        <v>1550.6513737872649</v>
+        <f t="shared" si="3"/>
+        <v>807.36116154179967</v>
       </c>
       <c r="E80" s="1">
-        <f>D80+B80+C80-Table3[[#This Row],[Снятие]]</f>
-        <v>267376.60116588982</v>
+        <f t="shared" si="4"/>
+        <v>139212.13171156461</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -3648,19 +3648,19 @@
         <v>18</v>
       </c>
       <c r="B81" s="1">
-        <f t="shared" si="12"/>
-        <v>267376.60116588982</v>
-      </c>
-      <c r="C81">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>139212.13171156461</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1500</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="13"/>
-        <v>1579.238506801024</v>
+        <f t="shared" si="3"/>
+        <v>820.82076831746031</v>
       </c>
       <c r="E81" s="1">
-        <f>D81+B81+C81-Table3[[#This Row],[Снятие]]</f>
-        <v>272305.83967269084</v>
+        <f t="shared" si="4"/>
+        <v>141532.95247988208</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>19</v>
       </c>
       <c r="B82" s="1">
-        <f t="shared" si="12"/>
-        <v>272305.83967269084</v>
-      </c>
-      <c r="C82">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>141532.95247988208</v>
+      </c>
+      <c r="C82" s="1">
+        <v>1500</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="13"/>
-        <v>1607.9923980906967</v>
+        <f t="shared" si="3"/>
+        <v>834.35888946597879</v>
       </c>
       <c r="E82" s="1">
-        <f>D82+B82+C82-Table3[[#This Row],[Снятие]]</f>
-        <v>277263.83207078156</v>
+        <f t="shared" si="4"/>
+        <v>143867.31136934806</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -3698,19 +3698,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="1">
-        <f t="shared" si="12"/>
-        <v>277263.83207078156</v>
-      </c>
-      <c r="C83">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>143867.31136934806</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1500</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="13"/>
-        <v>1636.9140204128926</v>
+        <f t="shared" si="3"/>
+        <v>847.97598298786374</v>
       </c>
       <c r="E83" s="1">
-        <f>D83+B83+C83-Table3[[#This Row],[Снятие]]</f>
-        <v>282250.74609119445</v>
+        <f t="shared" si="4"/>
+        <v>146215.28735233593</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -3723,19 +3723,19 @@
         <v>21</v>
       </c>
       <c r="B84" s="1">
-        <f t="shared" si="12"/>
-        <v>282250.74609119445</v>
-      </c>
-      <c r="C84">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>146215.28735233593</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1500</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="13"/>
-        <v>1666.0043521986345</v>
+        <f t="shared" si="3"/>
+        <v>861.672509555293</v>
       </c>
       <c r="E84" s="1">
-        <f>D84+B84+C84-Table3[[#This Row],[Снятие]]</f>
-        <v>287266.75044339307</v>
+        <f t="shared" si="4"/>
+        <v>148576.95986189123</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -3748,19 +3748,19 @@
         <v>22</v>
       </c>
       <c r="B85" s="1">
-        <f t="shared" si="12"/>
-        <v>287266.75044339307</v>
-      </c>
-      <c r="C85">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>148576.95986189123</v>
+      </c>
+      <c r="C85" s="1">
+        <v>1500</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" si="13"/>
-        <v>1695.2643775864597</v>
+        <f t="shared" si="3"/>
+        <v>875.44893252769884</v>
       </c>
       <c r="E85" s="1">
-        <f>D85+B85+C85-Table3[[#This Row],[Снятие]]</f>
-        <v>292312.01482097956</v>
+        <f t="shared" si="4"/>
+        <v>150952.40879441894</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -3773,19 +3773,19 @@
         <v>36</v>
       </c>
       <c r="B86" s="1">
-        <f t="shared" ref="B86:B97" si="14">E85</f>
-        <v>292312.01482097956</v>
-      </c>
-      <c r="C86">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>150952.40879441894</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1500</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" ref="D86:D97" si="15">(0.07/12)*(B86+C86)</f>
-        <v>1724.6950864557141</v>
+        <f t="shared" si="3"/>
+        <v>889.3057179674438</v>
       </c>
       <c r="E86" s="1">
-        <f>D86+B86+C86-Table3[[#This Row],[Снятие]]</f>
-        <v>297386.70990743529</v>
+        <f t="shared" si="4"/>
+        <v>153341.71451238639</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -3798,19 +3798,19 @@
         <v>12</v>
       </c>
       <c r="B87" s="1">
-        <f t="shared" si="14"/>
-        <v>297386.70990743529</v>
-      </c>
-      <c r="C87">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>153341.71451238639</v>
+      </c>
+      <c r="C87" s="1">
+        <v>1500</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" si="15"/>
-        <v>1754.2974744600392</v>
+        <f t="shared" si="3"/>
+        <v>903.24333465558732</v>
       </c>
       <c r="E87" s="1">
-        <f>D87+B87+C87-Table3[[#This Row],[Снятие]]</f>
-        <v>302491.00738189532</v>
+        <f t="shared" si="4"/>
+        <v>155744.95784704198</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -3823,19 +3823,19 @@
         <v>13</v>
       </c>
       <c r="B88" s="1">
-        <f t="shared" si="14"/>
-        <v>302491.00738189532</v>
-      </c>
-      <c r="C88">
-        <v>3350</v>
+        <f t="shared" si="5"/>
+        <v>155744.95784704198</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1500</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="15"/>
-        <v>1784.0725430610562</v>
+        <f t="shared" si="3"/>
+        <v>917.26225410774498</v>
       </c>
       <c r="E88" s="1">
-        <f>D88+B88+C88-Table3[[#This Row],[Снятие]]</f>
-        <v>307625.07992495637</v>
+        <f t="shared" si="4"/>
+        <v>158162.22010114972</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -3848,19 +3848,19 @@
         <v>14</v>
       </c>
       <c r="B89" s="1">
-        <f t="shared" si="14"/>
-        <v>307625.07992495637</v>
-      </c>
-      <c r="C89">
-        <v>12175</v>
+        <f t="shared" si="5"/>
+        <v>158162.22010114972</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1500</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="15"/>
-        <v>1865.5004662289123</v>
+        <f t="shared" si="3"/>
+        <v>931.3629505900401</v>
       </c>
       <c r="E89" s="1">
-        <f>D89+B89+C89-Table3[[#This Row],[Снятие]]</f>
-        <v>321665.5803911853</v>
+        <f t="shared" si="4"/>
+        <v>160593.58305173976</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -3877,19 +3877,19 @@
         <v>15</v>
       </c>
       <c r="B90" s="1">
-        <f t="shared" si="14"/>
-        <v>321665.5803911853</v>
-      </c>
-      <c r="C90">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>160593.58305173976</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1500</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="15"/>
-        <v>1897.0908856152478</v>
+        <f t="shared" si="3"/>
+        <v>945.5459011351486</v>
       </c>
       <c r="E90" s="1">
-        <f>D90+B90+C90-Table3[[#This Row],[Снятие]]</f>
-        <v>327112.67127680057</v>
+        <f t="shared" si="4"/>
+        <v>163039.12895287492</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -3902,19 +3902,19 @@
         <v>16</v>
       </c>
       <c r="B91" s="1">
-        <f t="shared" si="14"/>
-        <v>327112.67127680057</v>
-      </c>
-      <c r="C91">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>163039.12895287492</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1500</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="15"/>
-        <v>1928.8655824480034</v>
+        <f t="shared" si="3"/>
+        <v>959.81158555843706</v>
       </c>
       <c r="E91" s="1">
-        <f>D91+B91+C91-Table3[[#This Row],[Снятие]]</f>
-        <v>332591.53685924859</v>
+        <f t="shared" si="4"/>
+        <v>165498.94053843335</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -3927,19 +3927,19 @@
         <v>17</v>
       </c>
       <c r="B92" s="1">
-        <f t="shared" si="14"/>
-        <v>332591.53685924859</v>
-      </c>
-      <c r="C92">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>165498.94053843335</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1500</v>
       </c>
       <c r="D92" s="1">
-        <f t="shared" si="15"/>
-        <v>1960.8256316789502</v>
+        <f t="shared" si="3"/>
+        <v>974.16048647419461</v>
       </c>
       <c r="E92" s="1">
-        <f>D92+B92+C92-Table3[[#This Row],[Снятие]]</f>
-        <v>338102.36249092757</v>
+        <f t="shared" si="4"/>
+        <v>167973.10102490755</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -3952,19 +3952,19 @@
         <v>18</v>
       </c>
       <c r="B93" s="1">
-        <f t="shared" si="14"/>
-        <v>338102.36249092757</v>
-      </c>
-      <c r="C93">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>167973.10102490755</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1500</v>
       </c>
       <c r="D93" s="1">
-        <f t="shared" si="15"/>
-        <v>1992.9721145304109</v>
+        <f t="shared" si="3"/>
+        <v>988.59308931196074</v>
       </c>
       <c r="E93" s="1">
-        <f>D93+B93+C93-Table3[[#This Row],[Снятие]]</f>
-        <v>343645.33460545796</v>
+        <f t="shared" si="4"/>
+        <v>170461.69411421951</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -3977,19 +3977,19 @@
         <v>19</v>
       </c>
       <c r="B94" s="1">
-        <f t="shared" si="14"/>
-        <v>343645.33460545796</v>
-      </c>
-      <c r="C94">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>170461.69411421951</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1500</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" si="15"/>
-        <v>2025.3061185318381</v>
+        <f t="shared" si="3"/>
+        <v>1003.1098823329472</v>
       </c>
       <c r="E94" s="1">
-        <f>D94+B94+C94-Table3[[#This Row],[Снятие]]</f>
-        <v>349220.64072398981</v>
+        <f t="shared" si="4"/>
+        <v>172964.80399655245</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -4002,19 +4002,19 @@
         <v>20</v>
       </c>
       <c r="B95" s="1">
-        <f t="shared" si="14"/>
-        <v>349220.64072398981</v>
-      </c>
-      <c r="C95">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>172964.80399655245</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1500</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" si="15"/>
-        <v>2057.8287375566074</v>
+        <f t="shared" si="3"/>
+        <v>1017.7113566465561</v>
       </c>
       <c r="E95" s="1">
-        <f>D95+B95+C95-Table3[[#This Row],[Снятие]]</f>
-        <v>354828.4694615464</v>
+        <f t="shared" si="4"/>
+        <v>175482.51535319901</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -4027,19 +4027,19 @@
         <v>21</v>
       </c>
       <c r="B96" s="1">
-        <f t="shared" si="14"/>
-        <v>354828.4694615464</v>
-      </c>
-      <c r="C96">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>175482.51535319901</v>
+      </c>
+      <c r="C96" s="1">
+        <v>1500</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="15"/>
-        <v>2090.5410718590206</v>
+        <f t="shared" si="3"/>
+        <v>1032.3980062269943</v>
       </c>
       <c r="E96" s="1">
-        <f>D96+B96+C96-Table3[[#This Row],[Снятие]]</f>
-        <v>360469.01053340541</v>
+        <f t="shared" si="4"/>
+        <v>178014.91335942599</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -4052,19 +4052,19 @@
         <v>22</v>
       </c>
       <c r="B97" s="1">
-        <f t="shared" si="14"/>
-        <v>360469.01053340541</v>
-      </c>
-      <c r="C97">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>178014.91335942599</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1500</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" si="15"/>
-        <v>2123.4442281115316</v>
+        <f t="shared" si="3"/>
+        <v>1047.170327929985</v>
       </c>
       <c r="E97" s="1">
-        <f>D97+B97+C97-Table3[[#This Row],[Снятие]]</f>
-        <v>366142.45476151694</v>
+        <f t="shared" si="4"/>
+        <v>180562.08368735597</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -4077,19 +4077,19 @@
         <v>37</v>
       </c>
       <c r="B98" s="1">
-        <f t="shared" ref="B98:B109" si="16">E97</f>
-        <v>366142.45476151694</v>
-      </c>
-      <c r="C98">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>180562.08368735597</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1500</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" ref="D98:D109" si="17">(0.07/12)*(B98+C98)</f>
-        <v>2156.5393194421822</v>
+        <f t="shared" si="3"/>
+        <v>1062.0288215095766</v>
       </c>
       <c r="E98" s="1">
-        <f>D98+B98+C98-Table3[[#This Row],[Снятие]]</f>
-        <v>371848.99408095912</v>
+        <f t="shared" si="4"/>
+        <v>183124.11250886554</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -4102,19 +4102,19 @@
         <v>12</v>
       </c>
       <c r="B99" s="1">
-        <f t="shared" si="16"/>
-        <v>371848.99408095912</v>
-      </c>
-      <c r="C99">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>183124.11250886554</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1500</v>
       </c>
       <c r="D99" s="1">
-        <f t="shared" si="17"/>
-        <v>2189.8274654722618</v>
+        <f t="shared" si="3"/>
+        <v>1076.9739896350491</v>
       </c>
       <c r="E99" s="1">
-        <f>D99+B99+C99-Table3[[#This Row],[Снятие]]</f>
-        <v>377588.8215464314</v>
+        <f t="shared" si="4"/>
+        <v>185701.08649850058</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -4127,19 +4127,19 @@
         <v>13</v>
       </c>
       <c r="B100" s="1">
-        <f t="shared" si="16"/>
-        <v>377588.8215464314</v>
-      </c>
-      <c r="C100">
-        <v>3550</v>
+        <f t="shared" si="5"/>
+        <v>185701.08649850058</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1500</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" si="17"/>
-        <v>2223.3097923541832</v>
+        <f t="shared" si="3"/>
+        <v>1092.0063379079202</v>
       </c>
       <c r="E100" s="1">
-        <f>D100+B100+C100-Table3[[#This Row],[Снятие]]</f>
-        <v>383362.13133878558</v>
+        <f t="shared" si="4"/>
+        <v>188293.0928364085</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -4152,19 +4152,19 @@
         <v>14</v>
       </c>
       <c r="B101" s="1">
-        <f t="shared" si="16"/>
-        <v>383362.13133878558</v>
-      </c>
-      <c r="C101">
-        <v>12875</v>
+        <f t="shared" si="5"/>
+        <v>188293.0928364085</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1500</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="17"/>
-        <v>2311.383266142916</v>
+        <f t="shared" si="3"/>
+        <v>1107.1263748790495</v>
       </c>
       <c r="E101" s="1">
-        <f>D101+B101+C101-Table3[[#This Row],[Снятие]]</f>
-        <v>398548.5146049285</v>
+        <f t="shared" si="4"/>
+        <v>190900.21921128753</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -4181,19 +4181,19 @@
         <v>15</v>
       </c>
       <c r="B102" s="1">
-        <f t="shared" si="16"/>
-        <v>398548.5146049285</v>
-      </c>
-      <c r="C102">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>190900.21921128753</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1500</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" si="17"/>
-        <v>2346.7413351954165</v>
+        <f t="shared" si="3"/>
+        <v>1122.3346120658441</v>
       </c>
       <c r="E102" s="1">
-        <f>D102+B102+C102-Table3[[#This Row],[Снятие]]</f>
-        <v>404645.25594012393</v>
+        <f t="shared" si="4"/>
+        <v>193522.55382335337</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -4206,19 +4206,19 @@
         <v>16</v>
       </c>
       <c r="B103" s="1">
-        <f t="shared" si="16"/>
-        <v>404645.25594012393</v>
-      </c>
-      <c r="C103">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>193522.55382335337</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1500</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" si="17"/>
-        <v>2382.3056596507231</v>
+        <f t="shared" si="3"/>
+        <v>1137.6315639695613</v>
       </c>
       <c r="E103" s="1">
-        <f>D103+B103+C103-Table3[[#This Row],[Снятие]]</f>
-        <v>410777.56159977464</v>
+        <f t="shared" si="4"/>
+        <v>196160.18538732294</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -4231,19 +4231,19 @@
         <v>17</v>
       </c>
       <c r="B104" s="1">
-        <f t="shared" si="16"/>
-        <v>410777.56159977464</v>
-      </c>
-      <c r="C104">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>196160.18538732294</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1500</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" si="17"/>
-        <v>2418.077442665352</v>
+        <f t="shared" si="3"/>
+        <v>1153.0177480927173</v>
       </c>
       <c r="E104" s="1">
-        <f>D104+B104+C104-Table3[[#This Row],[Снятие]]</f>
-        <v>416945.63904243999</v>
+        <f t="shared" si="4"/>
+        <v>198813.20313541565</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -4256,19 +4256,19 @@
         <v>18</v>
       </c>
       <c r="B105" s="1">
-        <f t="shared" si="16"/>
-        <v>416945.63904243999</v>
-      </c>
-      <c r="C105">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>198813.20313541565</v>
+      </c>
+      <c r="C105" s="1">
+        <v>1500</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="17"/>
-        <v>2454.0578944142335</v>
+        <f t="shared" si="3"/>
+        <v>1168.4936849565913</v>
       </c>
       <c r="E105" s="1">
-        <f>D105+B105+C105-Table3[[#This Row],[Снятие]]</f>
-        <v>423149.69693685422</v>
+        <f t="shared" si="4"/>
+        <v>201481.69682037225</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -4281,19 +4281,19 @@
         <v>19</v>
       </c>
       <c r="B106" s="1">
-        <f t="shared" si="16"/>
-        <v>423149.69693685422</v>
-      </c>
-      <c r="C106">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>201481.69682037225</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1500</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="17"/>
-        <v>2490.2482321316497</v>
+        <f t="shared" si="3"/>
+        <v>1184.0598981188382</v>
       </c>
       <c r="E106" s="1">
-        <f>D106+B106+C106-Table3[[#This Row],[Снятие]]</f>
-        <v>429389.94516898587</v>
+        <f t="shared" si="4"/>
+        <v>204165.75671849109</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -4306,19 +4306,19 @@
         <v>20</v>
       </c>
       <c r="B107" s="1">
-        <f t="shared" si="16"/>
-        <v>429389.94516898587</v>
-      </c>
-      <c r="C107">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>204165.75671849109</v>
+      </c>
+      <c r="C107" s="1">
+        <v>1500</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="17"/>
-        <v>2526.6496801524177</v>
+        <f t="shared" si="3"/>
+        <v>1199.7169141911982</v>
       </c>
       <c r="E107" s="1">
-        <f>D107+B107+C107-Table3[[#This Row],[Снятие]]</f>
-        <v>435666.59484913829</v>
+        <f t="shared" si="4"/>
+        <v>206865.47363268229</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -4331,19 +4331,19 @@
         <v>21</v>
       </c>
       <c r="B108" s="1">
-        <f t="shared" si="16"/>
-        <v>435666.59484913829</v>
-      </c>
-      <c r="C108">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>206865.47363268229</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1500</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="17"/>
-        <v>2563.2634699533069</v>
+        <f t="shared" si="3"/>
+        <v>1215.4652628573135</v>
       </c>
       <c r="E108" s="1">
-        <f>D108+B108+C108-Table3[[#This Row],[Снятие]]</f>
-        <v>441979.85831909161</v>
+        <f t="shared" si="4"/>
+        <v>209580.93889553961</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -4356,19 +4356,19 @@
         <v>22</v>
       </c>
       <c r="B109" s="1">
-        <f t="shared" si="16"/>
-        <v>441979.85831909161</v>
-      </c>
-      <c r="C109">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>209580.93889553961</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1500</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="17"/>
-        <v>2600.0908401947013</v>
+        <f t="shared" si="3"/>
+        <v>1231.3054768906477</v>
       </c>
       <c r="E109" s="1">
-        <f>D109+B109+C109-Table3[[#This Row],[Снятие]]</f>
-        <v>448329.94915928633</v>
+        <f t="shared" si="4"/>
+        <v>212312.24437243026</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -4381,19 +4381,19 @@
         <v>38</v>
       </c>
       <c r="B110" s="1">
-        <f t="shared" ref="B110:B121" si="18">E109</f>
-        <v>448329.94915928633</v>
-      </c>
-      <c r="C110">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>212312.24437243026</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1500</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" ref="D110:D121" si="19">(0.07/12)*(B110+C110)</f>
-        <v>2637.1330367625037</v>
+        <f t="shared" si="3"/>
+        <v>1247.2380921725098</v>
       </c>
       <c r="E110" s="1">
-        <f>D110+B110+C110-Table3[[#This Row],[Снятие]]</f>
-        <v>454717.08219604881</v>
+        <f t="shared" si="4"/>
+        <v>215059.48246460277</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -4406,19 +4406,19 @@
         <v>12</v>
       </c>
       <c r="B111" s="1">
-        <f t="shared" si="18"/>
-        <v>454717.08219604881</v>
-      </c>
-      <c r="C111">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>215059.48246460277</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1500</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="19"/>
-        <v>2674.3913128102849</v>
+        <f t="shared" si="3"/>
+        <v>1263.2636477101828</v>
       </c>
       <c r="E111" s="1">
-        <f>D111+B111+C111-Table3[[#This Row],[Снятие]]</f>
-        <v>461141.47350885911</v>
+        <f t="shared" si="4"/>
+        <v>217822.74611231295</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -4431,19 +4431,19 @@
         <v>13</v>
       </c>
       <c r="B112" s="1">
-        <f t="shared" si="18"/>
-        <v>461141.47350885911</v>
-      </c>
-      <c r="C112">
-        <v>3750</v>
+        <f t="shared" si="5"/>
+        <v>217822.74611231295</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1500</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="19"/>
-        <v>2711.8669288016781</v>
+        <f t="shared" si="3"/>
+        <v>1279.3826856551589</v>
       </c>
       <c r="E112" s="1">
-        <f>D112+B112+C112-Table3[[#This Row],[Снятие]]</f>
-        <v>467603.34043766081</v>
+        <f t="shared" si="4"/>
+        <v>220602.12879796809</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -4456,19 +4456,19 @@
         <v>14</v>
       </c>
       <c r="B113" s="1">
-        <f t="shared" si="18"/>
-        <v>467603.34043766081</v>
-      </c>
-      <c r="C113">
-        <v>13575</v>
+        <f t="shared" si="5"/>
+        <v>220602.12879796809</v>
+      </c>
+      <c r="C113" s="1">
+        <v>1500</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="19"/>
-        <v>2806.8736525530217</v>
+        <f t="shared" si="3"/>
+        <v>1295.5957513214805</v>
       </c>
       <c r="E113" s="1">
-        <f>D113+B113+C113-Table3[[#This Row],[Снятие]]</f>
-        <v>483985.21409021382</v>
+        <f t="shared" si="4"/>
+        <v>223397.72454928956</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -4485,19 +4485,19 @@
         <v>15</v>
       </c>
       <c r="B114" s="1">
-        <f t="shared" si="18"/>
-        <v>483985.21409021382</v>
-      </c>
-      <c r="C114">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>223397.72454928956</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1500</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" si="19"/>
-        <v>2846.2887488595807</v>
+        <f t="shared" si="3"/>
+        <v>1311.9033932041891</v>
       </c>
       <c r="E114" s="1">
-        <f>D114+B114+C114-Table3[[#This Row],[Снятие]]</f>
-        <v>490781.50283907342</v>
+        <f t="shared" si="4"/>
+        <v>226209.62794249374</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -4510,19 +4510,19 @@
         <v>16</v>
       </c>
       <c r="B115" s="1">
-        <f t="shared" si="18"/>
-        <v>490781.50283907342</v>
-      </c>
-      <c r="C115">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>226209.62794249374</v>
+      </c>
+      <c r="C115" s="1">
+        <v>1500</v>
       </c>
       <c r="D115" s="1">
-        <f t="shared" si="19"/>
-        <v>2885.9337665612616</v>
+        <f t="shared" si="3"/>
+        <v>1328.3061629978802</v>
       </c>
       <c r="E115" s="1">
-        <f>D115+B115+C115-Table3[[#This Row],[Снятие]]</f>
-        <v>497617.43660563469</v>
+        <f t="shared" si="4"/>
+        <v>229037.93410549161</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -4535,19 +4535,19 @@
         <v>17</v>
       </c>
       <c r="B116" s="1">
-        <f t="shared" si="18"/>
-        <v>497617.43660563469</v>
-      </c>
-      <c r="C116">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>229037.93410549161</v>
+      </c>
+      <c r="C116" s="1">
+        <v>1500</v>
       </c>
       <c r="D116" s="1">
-        <f t="shared" si="19"/>
-        <v>2925.8100468662024</v>
+        <f t="shared" si="3"/>
+        <v>1344.8046156153678</v>
       </c>
       <c r="E116" s="1">
-        <f>D116+B116+C116-Table3[[#This Row],[Снятие]]</f>
-        <v>504493.24665250088</v>
+        <f t="shared" si="4"/>
+        <v>231882.73872110699</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -4560,19 +4560,19 @@
         <v>18</v>
       </c>
       <c r="B117" s="1">
-        <f t="shared" si="18"/>
-        <v>504493.24665250088</v>
-      </c>
-      <c r="C117">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>231882.73872110699</v>
+      </c>
+      <c r="C117" s="1">
+        <v>1500</v>
       </c>
       <c r="D117" s="1">
-        <f t="shared" si="19"/>
-        <v>2965.9189388062555</v>
+        <f t="shared" si="3"/>
+        <v>1361.3993092064575</v>
       </c>
       <c r="E117" s="1">
-        <f>D117+B117+C117-Table3[[#This Row],[Снятие]]</f>
-        <v>511409.16559130716</v>
+        <f t="shared" si="4"/>
+        <v>234744.13803031345</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -4585,19 +4585,19 @@
         <v>19</v>
       </c>
       <c r="B118" s="1">
-        <f t="shared" si="18"/>
-        <v>511409.16559130716</v>
-      </c>
-      <c r="C118">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>234744.13803031345</v>
+      </c>
+      <c r="C118" s="1">
+        <v>1500</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" si="19"/>
-        <v>3006.2617992826254</v>
+        <f t="shared" si="3"/>
+        <v>1378.0908051768286</v>
       </c>
       <c r="E118" s="1">
-        <f>D118+B118+C118-Table3[[#This Row],[Снятие]]</f>
-        <v>518365.42739058979</v>
+        <f t="shared" si="4"/>
+        <v>237622.22883549027</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
@@ -4610,19 +4610,19 @@
         <v>20</v>
       </c>
       <c r="B119" s="1">
-        <f t="shared" si="18"/>
-        <v>518365.42739058979</v>
-      </c>
-      <c r="C119">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>237622.22883549027</v>
+      </c>
+      <c r="C119" s="1">
+        <v>1500</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="19"/>
-        <v>3046.8399931117738</v>
+        <f t="shared" si="3"/>
+        <v>1394.8796682070267</v>
       </c>
       <c r="E119" s="1">
-        <f>D119+B119+C119-Table3[[#This Row],[Снятие]]</f>
-        <v>525362.26738370163</v>
+        <f t="shared" si="4"/>
+        <v>240517.10850369729</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -4635,19 +4635,19 @@
         <v>21</v>
       </c>
       <c r="B120" s="1">
-        <f t="shared" si="18"/>
-        <v>525362.26738370163</v>
-      </c>
-      <c r="C120">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>240517.10850369729</v>
+      </c>
+      <c r="C120" s="1">
+        <v>1500</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="19"/>
-        <v>3087.6548930715931</v>
+        <f t="shared" si="3"/>
+        <v>1411.7664662715677</v>
       </c>
       <c r="E120" s="1">
-        <f>D120+B120+C120-Table3[[#This Row],[Снятие]]</f>
-        <v>532399.92227677326</v>
+        <f t="shared" si="4"/>
+        <v>243428.87496996886</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -4660,19 +4660,19 @@
         <v>22</v>
       </c>
       <c r="B121" s="1">
-        <f t="shared" si="18"/>
-        <v>532399.92227677326</v>
-      </c>
-      <c r="C121">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>243428.87496996886</v>
+      </c>
+      <c r="C121" s="1">
+        <v>1500</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="19"/>
-        <v>3128.707879947844</v>
+        <f t="shared" si="3"/>
+        <v>1428.7517706581518</v>
       </c>
       <c r="E121" s="1">
-        <f>D121+B121+C121-Table3[[#This Row],[Снятие]]</f>
-        <v>539478.6301567211</v>
+        <f t="shared" si="4"/>
+        <v>246357.62674062702</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
@@ -4685,19 +4685,19 @@
         <v>39</v>
       </c>
       <c r="B122" s="1">
-        <f t="shared" ref="B122:B133" si="20">E121</f>
-        <v>539478.6301567211</v>
-      </c>
-      <c r="C122">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>246357.62674062702</v>
+      </c>
+      <c r="C122" s="1">
+        <v>1500</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" ref="D122:D133" si="21">(0.07/12)*(B122+C122)</f>
-        <v>3170.0003425808732</v>
+        <f t="shared" si="3"/>
+        <v>1445.8361559869911</v>
       </c>
       <c r="E122" s="1">
-        <f>D122+B122+C122-Table3[[#This Row],[Снятие]]</f>
-        <v>546598.63049930194</v>
+        <f t="shared" si="4"/>
+        <v>249303.46289661402</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         <v>12</v>
       </c>
       <c r="B123" s="1">
-        <f t="shared" si="20"/>
-        <v>546598.63049930194</v>
-      </c>
-      <c r="C123">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>249303.46289661402</v>
+      </c>
+      <c r="C123" s="1">
+        <v>1500</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="21"/>
-        <v>3211.5336779125946</v>
+        <f t="shared" si="3"/>
+        <v>1463.0202002302485</v>
       </c>
       <c r="E123" s="1">
-        <f>D123+B123+C123-Table3[[#This Row],[Снятие]]</f>
-        <v>553760.16417721449</v>
+        <f t="shared" si="4"/>
+        <v>252266.48309684425</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -4735,19 +4735,19 @@
         <v>13</v>
       </c>
       <c r="B124" s="1">
-        <f t="shared" si="20"/>
-        <v>553760.16417721449</v>
-      </c>
-      <c r="C124">
-        <v>3950</v>
+        <f t="shared" si="5"/>
+        <v>252266.48309684425</v>
+      </c>
+      <c r="C124" s="1">
+        <v>1500</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="21"/>
-        <v>3253.3092910337514</v>
+        <f t="shared" si="3"/>
+        <v>1480.3044847315916</v>
       </c>
       <c r="E124" s="1">
-        <f>D124+B124+C124-Table3[[#This Row],[Снятие]]</f>
-        <v>560963.47346824827</v>
+        <f t="shared" si="4"/>
+        <v>255246.78758157586</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
@@ -4760,19 +4760,19 @@
         <v>14</v>
       </c>
       <c r="B125" s="1">
-        <f t="shared" si="20"/>
-        <v>560963.47346824827</v>
-      </c>
-      <c r="C125">
-        <v>14275</v>
+        <f t="shared" si="5"/>
+        <v>255246.78758157586</v>
+      </c>
+      <c r="C125" s="1">
+        <v>1500</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" si="21"/>
-        <v>3355.5577618981151</v>
+        <f t="shared" si="3"/>
+        <v>1497.6895942258593</v>
       </c>
       <c r="E125" s="1">
-        <f>D125+B125+C125-Table3[[#This Row],[Снятие]]</f>
-        <v>578594.03123014641</v>
+        <f t="shared" si="4"/>
+        <v>258244.47717580173</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -4789,19 +4789,19 @@
         <v>15</v>
       </c>
       <c r="B126" s="1">
-        <f t="shared" si="20"/>
-        <v>578594.03123014641</v>
-      </c>
-      <c r="C126">
-        <v>4150</v>
+        <f t="shared" si="5"/>
+        <v>258244.47717580173</v>
+      </c>
+      <c r="C126" s="1">
+        <v>1500</v>
       </c>
       <c r="D126" s="1">
-        <f t="shared" si="21"/>
-        <v>3399.3401821758544</v>
+        <f t="shared" si="3"/>
+        <v>1515.1761168588434</v>
       </c>
       <c r="E126" s="1">
-        <f>D126+B126+C126-Table3[[#This Row],[Снятие]]</f>
-        <v>586143.37141232227</v>
+        <f t="shared" si="4"/>
+        <v>261259.65329266057</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -4814,19 +4814,19 @@
         <v>16</v>
       </c>
       <c r="B127" s="1">
-        <f t="shared" si="20"/>
-        <v>586143.37141232227</v>
-      </c>
-      <c r="C127">
-        <v>4150</v>
+        <f t="shared" si="5"/>
+        <v>261259.65329266057</v>
+      </c>
+      <c r="C127" s="1">
+        <v>1500</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" si="21"/>
-        <v>3443.3779999052135</v>
+        <f t="shared" si="3"/>
+        <v>1532.7646442071868</v>
       </c>
       <c r="E127" s="1">
-        <f>D127+B127+C127-Table3[[#This Row],[Снятие]]</f>
-        <v>593736.74941222754</v>
+        <f t="shared" si="4"/>
+        <v>264292.4179368678</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -4839,19 +4839,19 @@
         <v>17</v>
       </c>
       <c r="B128" s="1">
-        <f t="shared" si="20"/>
-        <v>593736.74941222754</v>
-      </c>
-      <c r="C128">
-        <v>4150</v>
+        <f t="shared" si="5"/>
+        <v>264292.4179368678</v>
+      </c>
+      <c r="C128" s="1">
+        <v>1500</v>
       </c>
       <c r="D128" s="1">
-        <f t="shared" si="21"/>
-        <v>3487.6727049046608</v>
+        <f t="shared" si="3"/>
+        <v>1550.4557712983956</v>
       </c>
       <c r="E128" s="1">
-        <f>D128+B128+C128-Table3[[#This Row],[Снятие]]</f>
-        <v>601374.42211713223</v>
+        <f t="shared" si="4"/>
+        <v>267342.87370816618</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -4864,19 +4864,19 @@
         <v>18</v>
       </c>
       <c r="B129" s="1">
-        <f t="shared" si="20"/>
-        <v>601374.42211713223</v>
-      </c>
-      <c r="C129">
-        <v>4150</v>
+        <f t="shared" si="5"/>
+        <v>267342.87370816618</v>
+      </c>
+      <c r="C129" s="1">
+        <v>1500</v>
       </c>
       <c r="D129" s="1">
-        <f t="shared" si="21"/>
-        <v>3532.2257956832714</v>
+        <f t="shared" si="3"/>
+        <v>1568.2500966309694</v>
       </c>
       <c r="E129" s="1">
-        <f>D129+B129+C129-Table3[[#This Row],[Снятие]]</f>
-        <v>609056.64791281545</v>
+        <f t="shared" si="4"/>
+        <v>270411.12380479713</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -4889,19 +4889,19 @@
         <v>19</v>
       </c>
       <c r="B130" s="1">
-        <f t="shared" si="20"/>
-        <v>609056.64791281545</v>
-      </c>
-      <c r="C130">
-        <v>4150</v>
+        <f t="shared" si="5"/>
+        <v>270411.12380479713</v>
+      </c>
+      <c r="C130" s="1">
+        <v>1500</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" si="21"/>
-        <v>3577.0387794914236</v>
+        <f t="shared" ref="D130:D169" si="6">(0.07/12)*(B130+C130)</f>
+        <v>1586.1482221946501</v>
       </c>
       <c r="E130" s="1">
-        <f>D130+B130+C130-Table3[[#This Row],[Снятие]]</f>
-        <v>616783.68669230689</v>
+        <f t="shared" si="4"/>
+        <v>273497.27202699176</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -4914,19 +4914,19 @@
         <v>20</v>
       </c>
       <c r="B131" s="1">
-        <f t="shared" si="20"/>
-        <v>616783.68669230689</v>
-      </c>
-      <c r="C131">
-        <v>4150</v>
+        <f t="shared" si="5"/>
+        <v>273497.27202699176</v>
+      </c>
+      <c r="C131" s="1">
+        <v>1500</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" si="21"/>
-        <v>3622.1131723717904</v>
+        <f t="shared" si="6"/>
+        <v>1604.1507534907853</v>
       </c>
       <c r="E131" s="1">
-        <f>D131+B131+C131-Table3[[#This Row],[Снятие]]</f>
-        <v>624555.79986467864</v>
+        <f t="shared" si="4"/>
+        <v>276601.42278048256</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -4939,19 +4939,19 @@
         <v>21</v>
       </c>
       <c r="B132" s="1">
-        <f t="shared" si="20"/>
-        <v>624555.79986467864</v>
-      </c>
-      <c r="C132">
-        <v>4150</v>
+        <f t="shared" si="5"/>
+        <v>276601.42278048256</v>
+      </c>
+      <c r="C132" s="1">
+        <v>1500</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" si="21"/>
-        <v>3667.4504992106254</v>
+        <f t="shared" si="6"/>
+        <v>1622.2582995528151</v>
       </c>
       <c r="E132" s="1">
-        <f>D132+B132+C132-Table3[[#This Row],[Снятие]]</f>
-        <v>632373.25036388927</v>
+        <f t="shared" ref="E132:E169" si="7">B132+C132+D132-F132</f>
+        <v>279723.6810800354</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -4964,19 +4964,19 @@
         <v>22</v>
       </c>
       <c r="B133" s="1">
-        <f t="shared" si="20"/>
-        <v>632373.25036388927</v>
-      </c>
-      <c r="C133">
-        <v>4150</v>
+        <f t="shared" ref="B133:B169" si="8">E132</f>
+        <v>279723.6810800354</v>
+      </c>
+      <c r="C133" s="1">
+        <v>1500</v>
       </c>
       <c r="D133" s="1">
-        <f t="shared" si="21"/>
-        <v>3713.0522937893543</v>
+        <f t="shared" si="6"/>
+        <v>1640.4714729668733</v>
       </c>
       <c r="E133" s="1">
-        <f>D133+B133+C133-Table3[[#This Row],[Снятие]]</f>
-        <v>640236.30265767861</v>
+        <f t="shared" si="7"/>
+        <v>282864.15255300229</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -4989,19 +4989,19 @@
         <v>40</v>
       </c>
       <c r="B134" s="1">
-        <f t="shared" ref="B134:B145" si="22">E133</f>
-        <v>640236.30265767861</v>
-      </c>
-      <c r="C134">
-        <v>4150</v>
+        <f t="shared" si="8"/>
+        <v>282864.15255300229</v>
+      </c>
+      <c r="C134" s="1">
+        <v>1500</v>
       </c>
       <c r="D134" s="1">
-        <f t="shared" ref="D134:D145" si="23">(0.07/12)*(B134+C134)</f>
-        <v>3758.9200988364587</v>
+        <f t="shared" si="6"/>
+        <v>1658.7908898925134</v>
       </c>
       <c r="E134" s="1">
-        <f>D134+B134+C134-Table3[[#This Row],[Снятие]]</f>
-        <v>648145.22275651502</v>
+        <f t="shared" si="7"/>
+        <v>286022.94344289479</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -5014,19 +5014,19 @@
         <v>12</v>
       </c>
       <c r="B135" s="1">
-        <f t="shared" si="22"/>
-        <v>648145.22275651502</v>
-      </c>
-      <c r="C135">
-        <v>4150</v>
+        <f t="shared" si="8"/>
+        <v>286022.94344289479</v>
+      </c>
+      <c r="C135" s="1">
+        <v>1500</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" si="23"/>
-        <v>3805.0554660796711</v>
+        <f t="shared" si="6"/>
+        <v>1677.2171700835529</v>
       </c>
       <c r="E135" s="1">
-        <f>D135+B135+C135-Table3[[#This Row],[Снятие]]</f>
-        <v>656100.27822259464</v>
+        <f t="shared" si="7"/>
+        <v>289200.16061297833</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -5039,19 +5039,19 @@
         <v>13</v>
       </c>
       <c r="B136" s="1">
-        <f t="shared" si="22"/>
-        <v>656100.27822259464</v>
-      </c>
-      <c r="C136">
-        <v>4150</v>
+        <f t="shared" si="8"/>
+        <v>289200.16061297833</v>
+      </c>
+      <c r="C136" s="1">
+        <v>1500</v>
       </c>
       <c r="D136" s="1">
-        <f t="shared" si="23"/>
-        <v>3851.459956298469</v>
+        <f t="shared" si="6"/>
+        <v>1695.7509369090403</v>
       </c>
       <c r="E136" s="1">
-        <f>D136+B136+C136-Table3[[#This Row],[Снятие]]</f>
-        <v>664101.73817889311</v>
+        <f t="shared" si="7"/>
+        <v>292395.91154988739</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -5064,19 +5064,19 @@
         <v>14</v>
       </c>
       <c r="B137" s="1">
-        <f t="shared" si="22"/>
-        <v>664101.73817889311</v>
-      </c>
-      <c r="C137">
-        <v>14975</v>
+        <f t="shared" si="8"/>
+        <v>292395.91154988739</v>
+      </c>
+      <c r="C137" s="1">
+        <v>1500</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" si="23"/>
-        <v>3961.2809727102099</v>
+        <f t="shared" si="6"/>
+        <v>1714.3928173743432</v>
       </c>
       <c r="E137" s="1">
-        <f>D137+B137+C137-Table3[[#This Row],[Снятие]]</f>
-        <v>683038.01915160334</v>
+        <f t="shared" si="7"/>
+        <v>295610.30436726171</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -5093,19 +5093,19 @@
         <v>15</v>
       </c>
       <c r="B138" s="1">
-        <f t="shared" si="22"/>
-        <v>683038.01915160334</v>
-      </c>
-      <c r="C138">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>295610.30436726171</v>
+      </c>
+      <c r="C138" s="1">
+        <v>1500</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" si="23"/>
-        <v>4009.7634450510195</v>
+        <f t="shared" si="6"/>
+        <v>1733.1434421423601</v>
       </c>
       <c r="E138" s="1">
-        <f>D138+B138+C138-Table3[[#This Row],[Снятие]]</f>
-        <v>691397.78259665438</v>
+        <f t="shared" si="7"/>
+        <v>298843.44780940405</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -5118,19 +5118,19 @@
         <v>16</v>
       </c>
       <c r="B139" s="1">
-        <f t="shared" si="22"/>
-        <v>691397.78259665438</v>
-      </c>
-      <c r="C139">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>298843.44780940405</v>
+      </c>
+      <c r="C139" s="1">
+        <v>1500</v>
       </c>
       <c r="D139" s="1">
-        <f t="shared" si="23"/>
-        <v>4058.5287318138176</v>
+        <f t="shared" si="6"/>
+        <v>1752.0034455548571</v>
       </c>
       <c r="E139" s="1">
-        <f>D139+B139+C139-Table3[[#This Row],[Снятие]]</f>
-        <v>699806.31132846815</v>
+        <f t="shared" si="7"/>
+        <v>302095.45125495893</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
@@ -5143,19 +5143,19 @@
         <v>17</v>
       </c>
       <c r="B140" s="1">
-        <f t="shared" si="22"/>
-        <v>699806.31132846815</v>
-      </c>
-      <c r="C140">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>302095.45125495893</v>
+      </c>
+      <c r="C140" s="1">
+        <v>1500</v>
       </c>
       <c r="D140" s="1">
-        <f t="shared" si="23"/>
-        <v>4107.5784827493981</v>
+        <f t="shared" si="6"/>
+        <v>1770.9734656539272</v>
       </c>
       <c r="E140" s="1">
-        <f>D140+B140+C140-Table3[[#This Row],[Снятие]]</f>
-        <v>708263.88981121755</v>
+        <f t="shared" si="7"/>
+        <v>305366.42472061288</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -5168,19 +5168,19 @@
         <v>18</v>
       </c>
       <c r="B141" s="1">
-        <f t="shared" si="22"/>
-        <v>708263.88981121755</v>
-      </c>
-      <c r="C141">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>305366.42472061288</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1500</v>
       </c>
       <c r="D141" s="1">
-        <f t="shared" si="23"/>
-        <v>4156.9143572321027</v>
+        <f t="shared" si="6"/>
+        <v>1790.0541442035751</v>
       </c>
       <c r="E141" s="1">
-        <f>D141+B141+C141-Table3[[#This Row],[Снятие]]</f>
-        <v>716770.8041684496</v>
+        <f t="shared" si="7"/>
+        <v>308656.47886481642</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -5193,19 +5193,19 @@
         <v>19</v>
       </c>
       <c r="B142" s="1">
-        <f t="shared" si="22"/>
-        <v>716770.8041684496</v>
-      </c>
-      <c r="C142">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>308656.47886481642</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1500</v>
       </c>
       <c r="D142" s="1">
-        <f t="shared" si="23"/>
-        <v>4206.5380243159561</v>
+        <f t="shared" si="6"/>
+        <v>1809.2461267114293</v>
       </c>
       <c r="E142" s="1">
-        <f>D142+B142+C142-Table3[[#This Row],[Снятие]]</f>
-        <v>725327.34219276556</v>
+        <f t="shared" si="7"/>
+        <v>311965.72499152785</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -5218,19 +5218,19 @@
         <v>20</v>
       </c>
       <c r="B143" s="1">
-        <f t="shared" si="22"/>
-        <v>725327.34219276556</v>
-      </c>
-      <c r="C143">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>311965.72499152785</v>
+      </c>
+      <c r="C143" s="1">
+        <v>1500</v>
       </c>
       <c r="D143" s="1">
-        <f t="shared" si="23"/>
-        <v>4256.4511627911324</v>
+        <f t="shared" si="6"/>
+        <v>1828.5500624505792</v>
       </c>
       <c r="E143" s="1">
-        <f>D143+B143+C143-Table3[[#This Row],[Снятие]]</f>
-        <v>733933.79335555667</v>
+        <f t="shared" si="7"/>
+        <v>315294.27505397843</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -5243,19 +5243,19 @@
         <v>21</v>
       </c>
       <c r="B144" s="1">
-        <f t="shared" si="22"/>
-        <v>733933.79335555667</v>
-      </c>
-      <c r="C144">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>315294.27505397843</v>
+      </c>
+      <c r="C144" s="1">
+        <v>1500</v>
       </c>
       <c r="D144" s="1">
-        <f>(0.07/12)*(B144+C144)</f>
-        <v>4306.6554612407472</v>
+        <f t="shared" si="6"/>
+        <v>1847.966604481541</v>
       </c>
       <c r="E144" s="1">
-        <f>D144+B144+C144-Table3[[#This Row],[Снятие]]</f>
-        <v>742590.44881679746</v>
+        <f t="shared" si="7"/>
+        <v>318642.24165846</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -5268,19 +5268,19 @@
         <v>22</v>
       </c>
       <c r="B145" s="1">
-        <f t="shared" si="22"/>
-        <v>742590.44881679746</v>
-      </c>
-      <c r="C145">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>318642.24165846</v>
+      </c>
+      <c r="C145" s="1">
+        <v>1500</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" si="23"/>
-        <v>4357.1526180979854</v>
+        <f t="shared" si="6"/>
+        <v>1867.4964096743502</v>
       </c>
       <c r="E145" s="1">
-        <f>D145+B145+C145-Table3[[#This Row],[Снятие]]</f>
-        <v>751297.60143489542</v>
+        <f t="shared" si="7"/>
+        <v>322009.73806813435</v>
       </c>
       <c r="F145" s="1">
         <v>0</v>
@@ -5293,19 +5293,19 @@
         <v>41</v>
       </c>
       <c r="B146" s="1">
-        <f t="shared" ref="B146:B157" si="24">E145</f>
-        <v>751297.60143489542</v>
-      </c>
-      <c r="C146">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>322009.73806813435</v>
+      </c>
+      <c r="C146" s="1">
+        <v>1500</v>
       </c>
       <c r="D146" s="1">
-        <f t="shared" ref="D146:D157" si="25">(0.07/12)*(B146+C146)</f>
-        <v>4407.9443417035573</v>
+        <f t="shared" si="6"/>
+        <v>1887.1401387307837</v>
       </c>
       <c r="E146" s="1">
-        <f>D146+B146+C146-Table3[[#This Row],[Снятие]]</f>
-        <v>760055.54577659897</v>
+        <f t="shared" si="7"/>
+        <v>325396.87820686511</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -5318,19 +5318,19 @@
         <v>12</v>
       </c>
       <c r="B147" s="1">
-        <f t="shared" si="24"/>
-        <v>760055.54577659897</v>
-      </c>
-      <c r="C147">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>325396.87820686511</v>
+      </c>
+      <c r="C147" s="1">
+        <v>1500</v>
       </c>
       <c r="D147" s="1">
-        <f t="shared" si="25"/>
-        <v>4459.0323503634945</v>
+        <f t="shared" si="6"/>
+        <v>1906.8984562067133</v>
       </c>
       <c r="E147" s="1">
-        <f>D147+B147+C147-Table3[[#This Row],[Снятие]]</f>
-        <v>768864.57812696241</v>
+        <f t="shared" si="7"/>
+        <v>328803.77666307183</v>
       </c>
       <c r="F147" s="1">
         <v>0</v>
@@ -5343,19 +5343,19 @@
         <v>13</v>
       </c>
       <c r="B148" s="1">
-        <f t="shared" si="24"/>
-        <v>768864.57812696241</v>
-      </c>
-      <c r="C148">
-        <v>4350</v>
+        <f t="shared" si="8"/>
+        <v>328803.77666307183</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1500</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" si="25"/>
-        <v>4510.4183724072809</v>
+        <f t="shared" si="6"/>
+        <v>1926.7720305345858</v>
       </c>
       <c r="E148" s="1">
-        <f>D148+B148+C148-Table3[[#This Row],[Снятие]]</f>
-        <v>777724.99649936974</v>
+        <f t="shared" si="7"/>
+        <v>332230.5486936064</v>
       </c>
       <c r="F148" s="1">
         <v>0</v>
@@ -5368,19 +5368,19 @@
         <v>14</v>
       </c>
       <c r="B149" s="1">
-        <f t="shared" si="24"/>
-        <v>777724.99649936974</v>
-      </c>
-      <c r="C149">
-        <v>15675</v>
+        <f t="shared" si="8"/>
+        <v>332230.5486936064</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1500</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="25"/>
-        <v>4628.1666462463236</v>
+        <f t="shared" si="6"/>
+        <v>1946.7615340460375</v>
       </c>
       <c r="E149" s="1">
-        <f>D149+B149+C149-Table3[[#This Row],[Снятие]]</f>
-        <v>798028.16314561607</v>
+        <f t="shared" si="7"/>
+        <v>335677.31022765243</v>
       </c>
       <c r="F149" s="1">
         <v>0</v>
@@ -5397,19 +5397,19 @@
         <v>15</v>
       </c>
       <c r="B150" s="1">
-        <f t="shared" si="24"/>
-        <v>798028.16314561607</v>
-      </c>
-      <c r="C150">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>335677.31022765243</v>
+      </c>
+      <c r="C150" s="1">
+        <v>1500</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="25"/>
-        <v>4681.7059516827603</v>
+        <f t="shared" si="6"/>
+        <v>1966.8676429946393</v>
       </c>
       <c r="E150" s="1">
-        <f>D150+B150+C150-Table3[[#This Row],[Снятие]]</f>
-        <v>807259.86909729883</v>
+        <f t="shared" si="7"/>
+        <v>339144.17787064705</v>
       </c>
       <c r="F150" s="1">
         <v>0</v>
@@ -5422,19 +5422,19 @@
         <v>16</v>
       </c>
       <c r="B151" s="1">
-        <f t="shared" si="24"/>
-        <v>807259.86909729883</v>
-      </c>
-      <c r="C151">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>339144.17787064705</v>
+      </c>
+      <c r="C151" s="1">
+        <v>1500</v>
       </c>
       <c r="D151" s="1">
-        <f t="shared" si="25"/>
-        <v>4735.5575697342438</v>
+        <f t="shared" si="6"/>
+        <v>1987.0910375787746</v>
       </c>
       <c r="E151" s="1">
-        <f>D151+B151+C151-Table3[[#This Row],[Снятие]]</f>
-        <v>816545.42666703311</v>
+        <f t="shared" si="7"/>
+        <v>342631.26890822581</v>
       </c>
       <c r="F151" s="1">
         <v>0</v>
@@ -5447,19 +5447,19 @@
         <v>17</v>
       </c>
       <c r="B152" s="1">
-        <f t="shared" si="24"/>
-        <v>816545.42666703311</v>
-      </c>
-      <c r="C152">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>342631.26890822581</v>
+      </c>
+      <c r="C152" s="1">
+        <v>1500</v>
       </c>
       <c r="D152" s="1">
-        <f t="shared" si="25"/>
-        <v>4789.7233222243603</v>
+        <f t="shared" si="6"/>
+        <v>2007.4324019646506</v>
       </c>
       <c r="E152" s="1">
-        <f>D152+B152+C152-Table3[[#This Row],[Снятие]]</f>
-        <v>825885.14998925745</v>
+        <f t="shared" si="7"/>
+        <v>346138.70131019049</v>
       </c>
       <c r="F152" s="1">
         <v>0</v>
@@ -5472,19 +5472,19 @@
         <v>18</v>
       </c>
       <c r="B153" s="1">
-        <f t="shared" si="24"/>
-        <v>825885.14998925745</v>
-      </c>
-      <c r="C153">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>346138.70131019049</v>
+      </c>
+      <c r="C153" s="1">
+        <v>1500</v>
       </c>
       <c r="D153" s="1">
-        <f t="shared" si="25"/>
-        <v>4844.205041604002</v>
+        <f t="shared" si="6"/>
+        <v>2027.8924243094446</v>
       </c>
       <c r="E153" s="1">
-        <f>D153+B153+C153-Table3[[#This Row],[Снятие]]</f>
-        <v>835279.35503086145</v>
+        <f t="shared" si="7"/>
+        <v>349666.59373449994</v>
       </c>
       <c r="F153" s="1">
         <v>0</v>
@@ -5497,19 +5497,19 @@
         <v>19</v>
       </c>
       <c r="B154" s="1">
-        <f t="shared" si="24"/>
-        <v>835279.35503086145</v>
-      </c>
-      <c r="C154">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>349666.59373449994</v>
+      </c>
+      <c r="C154" s="1">
+        <v>1500</v>
       </c>
       <c r="D154" s="1">
-        <f t="shared" si="25"/>
-        <v>4899.0045710133591</v>
+        <f t="shared" si="6"/>
+        <v>2048.4717967845831</v>
       </c>
       <c r="E154" s="1">
-        <f>D154+B154+C154-Table3[[#This Row],[Снятие]]</f>
-        <v>844728.35960187484</v>
+        <f t="shared" si="7"/>
+        <v>353215.06553128455</v>
       </c>
       <c r="F154" s="1">
         <v>0</v>
@@ -5522,19 +5522,19 @@
         <v>20</v>
       </c>
       <c r="B155" s="1">
-        <f t="shared" si="24"/>
-        <v>844728.35960187484</v>
-      </c>
-      <c r="C155">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>353215.06553128455</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1500</v>
       </c>
       <c r="D155" s="1">
-        <f t="shared" si="25"/>
-        <v>4954.1237643442701</v>
+        <f t="shared" si="6"/>
+        <v>2069.17121559916</v>
       </c>
       <c r="E155" s="1">
-        <f>D155+B155+C155-Table3[[#This Row],[Снятие]]</f>
-        <v>854232.48336621909</v>
+        <f t="shared" si="7"/>
+        <v>356784.23674688372</v>
       </c>
       <c r="F155" s="1">
         <v>0</v>
@@ -5547,19 +5547,19 @@
         <v>21</v>
       </c>
       <c r="B156" s="1">
-        <f t="shared" si="24"/>
-        <v>854232.48336621909</v>
-      </c>
-      <c r="C156">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>356784.23674688372</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1500</v>
       </c>
       <c r="D156" s="1">
-        <f t="shared" si="25"/>
-        <v>5009.5644863029447</v>
+        <f t="shared" si="6"/>
+        <v>2089.9913810234884</v>
       </c>
       <c r="E156" s="1">
-        <f>D156+B156+C156-Table3[[#This Row],[Снятие]]</f>
-        <v>863792.047852522</v>
+        <f t="shared" si="7"/>
+        <v>360374.2281279072</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -5572,19 +5572,19 @@
         <v>22</v>
       </c>
       <c r="B157" s="1">
-        <f t="shared" si="24"/>
-        <v>863792.047852522</v>
-      </c>
-      <c r="C157">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>360374.2281279072</v>
+      </c>
+      <c r="C157" s="1">
+        <v>1500</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" si="25"/>
-        <v>5065.3286124730448</v>
+        <f t="shared" si="6"/>
+        <v>2110.9329974127922</v>
       </c>
       <c r="E157" s="1">
-        <f>D157+B157+C157-Table3[[#This Row],[Снятие]]</f>
-        <v>873407.37646499509</v>
+        <f t="shared" si="7"/>
+        <v>363985.16112532001</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -5597,19 +5597,19 @@
         <v>43</v>
       </c>
       <c r="B158" s="1">
-        <f t="shared" ref="B158:B169" si="26">E157</f>
-        <v>873407.37646499509</v>
-      </c>
-      <c r="C158">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>363985.16112532001</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1500</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" ref="D158:D169" si="27">(0.07/12)*(B158+C158)</f>
-        <v>5121.4180293791378</v>
+        <f t="shared" si="6"/>
+        <v>2131.9967732310333</v>
       </c>
       <c r="E158" s="1">
-        <f>D158+B158+C158-Table3[[#This Row],[Снятие]]</f>
-        <v>883078.79449437419</v>
+        <f t="shared" si="7"/>
+        <v>367617.15789855103</v>
       </c>
       <c r="F158" s="1">
         <v>0</v>
@@ -5622,19 +5622,19 @@
         <v>12</v>
       </c>
       <c r="B159" s="1">
-        <f t="shared" si="26"/>
-        <v>883078.79449437419</v>
-      </c>
-      <c r="C159">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>367617.15789855103</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1500</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="27"/>
-        <v>5177.8346345505161</v>
+        <f t="shared" si="6"/>
+        <v>2153.1834210748812</v>
       </c>
       <c r="E159" s="1">
-        <f>D159+B159+C159-Table3[[#This Row],[Снятие]]</f>
-        <v>892806.62912892469</v>
+        <f t="shared" si="7"/>
+        <v>371270.34131962591</v>
       </c>
       <c r="F159" s="1">
         <v>0</v>
@@ -5647,19 +5647,19 @@
         <v>13</v>
       </c>
       <c r="B160" s="1">
-        <f t="shared" si="26"/>
-        <v>892806.62912892469</v>
-      </c>
-      <c r="C160">
-        <v>4550</v>
+        <f t="shared" si="8"/>
+        <v>371270.34131962591</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1500</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="27"/>
-        <v>5234.5803365853944</v>
+        <f t="shared" si="6"/>
+        <v>2174.493657697818</v>
       </c>
       <c r="E160" s="1">
-        <f>D160+B160+C160-Table3[[#This Row],[Снятие]]</f>
-        <v>902591.2094655101</v>
+        <f t="shared" si="7"/>
+        <v>374944.83497732371</v>
       </c>
       <c r="F160" s="1">
         <v>0</v>
@@ -5672,19 +5672,19 @@
         <v>14</v>
       </c>
       <c r="B161" s="1">
-        <f t="shared" si="26"/>
-        <v>902591.2094655101</v>
-      </c>
-      <c r="C161">
-        <v>16375</v>
+        <f t="shared" si="8"/>
+        <v>374944.83497732371</v>
+      </c>
+      <c r="C161" s="1">
+        <v>1500</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="27"/>
-        <v>5360.6362218821423</v>
+        <f t="shared" si="6"/>
+        <v>2195.9282040343883</v>
       </c>
       <c r="E161" s="1">
-        <f>D161+B161+C161-Table3[[#This Row],[Снятие]]</f>
-        <v>924326.84568739228</v>
+        <f t="shared" si="7"/>
+        <v>378640.76318135811</v>
       </c>
       <c r="F161" s="1">
         <v>0</v>
@@ -5701,19 +5701,19 @@
         <v>15</v>
       </c>
       <c r="B162" s="1">
-        <f t="shared" si="26"/>
-        <v>924326.84568739228</v>
-      </c>
-      <c r="C162">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>378640.76318135811</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1500</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" si="27"/>
-        <v>5419.6149331764555</v>
+        <f t="shared" si="6"/>
+        <v>2217.4877852245891</v>
       </c>
       <c r="E162" s="1">
-        <f>D162+B162+C162-Table3[[#This Row],[Снятие]]</f>
-        <v>934496.46062056872</v>
+        <f t="shared" si="7"/>
+        <v>382358.25096658268</v>
       </c>
       <c r="F162" s="1">
         <v>0</v>
@@ -5726,19 +5726,19 @@
         <v>16</v>
       </c>
       <c r="B163" s="1">
-        <f t="shared" si="26"/>
-        <v>934496.46062056872</v>
-      </c>
-      <c r="C163">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>382358.25096658268</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1500</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" si="27"/>
-        <v>5478.937686953318</v>
+        <f t="shared" si="6"/>
+        <v>2239.173130638399</v>
       </c>
       <c r="E163" s="1">
-        <f>D163+B163+C163-Table3[[#This Row],[Снятие]]</f>
-        <v>944725.39830752206</v>
+        <f t="shared" si="7"/>
+        <v>386097.42409722105</v>
       </c>
       <c r="F163" s="1">
         <v>0</v>
@@ -5751,19 +5751,19 @@
         <v>17</v>
       </c>
       <c r="B164" s="1">
-        <f t="shared" si="26"/>
-        <v>944725.39830752206</v>
-      </c>
-      <c r="C164">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>386097.42409722105</v>
+      </c>
+      <c r="C164" s="1">
+        <v>1500</v>
       </c>
       <c r="D164" s="1">
-        <f t="shared" si="27"/>
-        <v>5538.6064901272121</v>
+        <f t="shared" si="6"/>
+        <v>2260.9849739004562</v>
       </c>
       <c r="E164" s="1">
-        <f>D164+B164+C164-Table3[[#This Row],[Снятие]]</f>
-        <v>955014.00479764922</v>
+        <f t="shared" si="7"/>
+        <v>389858.40907112148</v>
       </c>
       <c r="F164" s="1">
         <v>0</v>
@@ -5776,19 +5776,19 @@
         <v>18</v>
       </c>
       <c r="B165" s="1">
-        <f t="shared" si="26"/>
-        <v>955014.00479764922</v>
-      </c>
-      <c r="C165">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>389858.40907112148</v>
+      </c>
+      <c r="C165" s="1">
+        <v>1500</v>
       </c>
       <c r="D165" s="1">
-        <f t="shared" si="27"/>
-        <v>5598.6233613196209</v>
+        <f t="shared" si="6"/>
+        <v>2282.9240529148756</v>
       </c>
       <c r="E165" s="1">
-        <f>D165+B165+C165-Table3[[#This Row],[Снятие]]</f>
-        <v>965362.62815896887</v>
+        <f t="shared" si="7"/>
+        <v>393641.33312403638</v>
       </c>
       <c r="F165" s="1">
         <v>0</v>
@@ -5801,19 +5801,19 @@
         <v>19</v>
       </c>
       <c r="B166" s="1">
-        <f t="shared" si="26"/>
-        <v>965362.62815896887</v>
-      </c>
-      <c r="C166">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>393641.33312403638</v>
+      </c>
+      <c r="C166" s="1">
+        <v>1500</v>
       </c>
       <c r="D166" s="1">
-        <f t="shared" si="27"/>
-        <v>5658.9903309273186</v>
+        <f t="shared" si="6"/>
+        <v>2304.9911098902121</v>
       </c>
       <c r="E166" s="1">
-        <f>D166+B166+C166-Table3[[#This Row],[Снятие]]</f>
-        <v>975771.61848989618</v>
+        <f t="shared" si="7"/>
+        <v>397446.3242339266</v>
       </c>
       <c r="F166" s="1">
         <v>0</v>
@@ -5826,19 +5826,19 @@
         <v>20</v>
       </c>
       <c r="B167" s="1">
-        <f t="shared" si="26"/>
-        <v>975771.61848989618</v>
-      </c>
-      <c r="C167">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>397446.3242339266</v>
+      </c>
+      <c r="C167" s="1">
+        <v>1500</v>
       </c>
       <c r="D167" s="1">
-        <f t="shared" si="27"/>
-        <v>5719.7094411910612</v>
+        <f t="shared" si="6"/>
+        <v>2327.1868913645721</v>
       </c>
       <c r="E167" s="1">
-        <f>D167+B167+C167-Table3[[#This Row],[Снятие]]</f>
-        <v>986241.32793108723</v>
+        <f t="shared" si="7"/>
+        <v>401273.51112529117</v>
       </c>
       <c r="F167" s="1">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         <v>21</v>
       </c>
       <c r="B168" s="1">
-        <f t="shared" si="26"/>
-        <v>986241.32793108723</v>
-      </c>
-      <c r="C168">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>401273.51112529117</v>
+      </c>
+      <c r="C168" s="1">
+        <v>1500</v>
       </c>
       <c r="D168" s="1">
-        <f t="shared" si="27"/>
-        <v>5780.7827462646756</v>
+        <f t="shared" si="6"/>
+        <v>2349.5121482308655</v>
       </c>
       <c r="E168" s="1">
-        <f>D168+B168+C168-Table3[[#This Row],[Снятие]]</f>
-        <v>996772.11067735194</v>
+        <f t="shared" si="7"/>
+        <v>405123.02327352203</v>
       </c>
       <c r="F168" s="1">
         <v>0</v>
@@ -5876,19 +5876,19 @@
         <v>22</v>
       </c>
       <c r="B169" s="1">
-        <f t="shared" si="26"/>
-        <v>996772.11067735194</v>
-      </c>
-      <c r="C169">
-        <v>4750</v>
+        <f t="shared" si="8"/>
+        <v>405123.02327352203</v>
+      </c>
+      <c r="C169" s="1">
+        <v>1500</v>
       </c>
       <c r="D169" s="1">
-        <f t="shared" si="27"/>
-        <v>5842.2123122845533</v>
+        <f t="shared" si="6"/>
+        <v>2371.967635762212</v>
       </c>
       <c r="E169" s="1">
-        <f>D169+B169+C169-Table3[[#This Row],[Снятие]]</f>
-        <v>1007364.3229896365</v>
+        <f t="shared" si="7"/>
+        <v>408994.99090928427</v>
       </c>
       <c r="F169" s="1">
         <v>0</v>
@@ -5899,6 +5899,9 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="B2 E3 E4:E169" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -25951,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="F835" s="1">
-        <f t="shared" ref="F835:F875" si="40">B835+D835-E835</f>
+        <f t="shared" ref="F835:F870" si="40">B835+D835-E835</f>
         <v>1303.929420770186</v>
       </c>
     </row>
@@ -25960,7 +25963,7 @@
         <v>46889</v>
       </c>
       <c r="B836" s="1">
-        <f t="shared" ref="B836:B875" si="41">F835</f>
+        <f t="shared" ref="B836:B870" si="41">F835</f>
         <v>1303.929420770186</v>
       </c>
       <c r="C836">
@@ -26348,7 +26351,7 @@
         <v>658.50011848373595</v>
       </c>
       <c r="C852">
-        <f t="shared" ref="C852:C875" si="42">(12.9%/365)</f>
+        <f t="shared" ref="C852:C870" si="42">(12.9%/365)</f>
         <v>3.5342465753424658E-4</v>
       </c>
       <c r="D852" s="1">
